--- a/docs/Podium_WBS_v0_3.xlsx
+++ b/docs/Podium_WBS_v0_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/onzimi/Desktop/GitHub/Podium/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C363EE-1961-FA4E-8F9C-CB4C1A1969F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8974EC28-108B-E047-80A6-C203A03B371F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,7 +357,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="577">
   <si>
     <t>WBS</t>
   </si>
@@ -1572,9 +1572,6 @@
   </si>
   <si>
     <t>1.4</t>
-  </si>
-  <si>
-    <t>2.0</t>
   </si>
   <si>
     <t>2.1</t>
@@ -3025,9 +3022,18 @@
     <xf numFmtId="0" fontId="34" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3036,18 +3042,7 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3059,6 +3054,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3068,43 +3075,11 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
-    <dxf>
-      <font>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF1D4ED8"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3253,7 +3228,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFD6E4FB"/>
+          <bgColor rgb="FFCFEBCF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3309,7 +3284,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFCFEBCF"/>
+          <bgColor rgb="FFD6E4FB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3365,6 +3340,28 @@
         <i val="0"/>
         <color rgb="FFDC2626"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1D4ED8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3737,25 +3734,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:221" ht="20">
-      <c r="A1" s="108" t="s">
-        <v>395</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
+      <c r="A1" s="90" t="s">
+        <v>394</v>
+      </c>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
     </row>
     <row r="3" spans="1:221">
       <c r="A3" s="76" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C3" s="77"/>
       <c r="D3" s="77"/>
@@ -3764,24 +3761,24 @@
       </c>
       <c r="F3" s="78">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46282</v>
       </c>
       <c r="G3" s="79" t="s">
         <v>244</v>
       </c>
       <c r="H3" s="80">
         <f ca="1">IFERROR(AVERAGEIFS($G$10:$G$152,$C$10:$C$152,"&lt;&gt;",$H$10:$H$152,"&lt;&gt;삭제"),0)</f>
-        <v>0.547602400728183</v>
+        <v>0.59563829787234046</v>
       </c>
       <c r="I3" s="77"/>
       <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:221">
       <c r="A4" s="76" t="s">
+        <v>566</v>
+      </c>
+      <c r="B4" s="77" t="s">
         <v>567</v>
-      </c>
-      <c r="B4" s="77" t="s">
-        <v>568</v>
       </c>
       <c r="C4" s="77"/>
       <c r="D4" s="77"/>
@@ -3803,13 +3800,13 @@
         <v>209</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E5" s="57" t="s">
+        <v>396</v>
+      </c>
+      <c r="F5" s="58" t="s">
         <v>397</v>
-      </c>
-      <c r="F5" s="58" t="s">
-        <v>398</v>
       </c>
       <c r="G5" s="77"/>
       <c r="H5" s="77"/>
@@ -3818,7 +3815,7 @@
     </row>
     <row r="6" spans="1:221">
       <c r="A6" s="77" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B6" s="77"/>
       <c r="C6" s="77"/>
@@ -4598,7 +4595,7 @@
         <v/>
       </c>
       <c r="GV6" s="69" t="str">
-        <f t="shared" ref="GV6:JG6" si="3">IF(OR(GV7=$L$7,DAY(GV7)=1),TEXT(GV7,"m월"),"")</f>
+        <f t="shared" ref="GV6:HM6" si="3">IF(OR(GV7=$L$7,DAY(GV7)=1),TEXT(GV7,"m월"),"")</f>
         <v/>
       </c>
       <c r="GW6" s="69" t="str">
@@ -5538,10 +5535,10 @@
         <v>270</v>
       </c>
       <c r="I8" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="J8" s="82" t="s">
         <v>399</v>
-      </c>
-      <c r="J8" s="82" t="s">
-        <v>400</v>
       </c>
       <c r="L8" s="71" t="str">
         <f t="shared" ref="L8:BW8" si="8">TEXT(L$7,"aaa")</f>
@@ -6386,7 +6383,7 @@
     </row>
     <row r="9" spans="1:221">
       <c r="A9" s="73" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B9" s="48"/>
       <c r="C9" s="48"/>
@@ -6399,7 +6396,7 @@
       <c r="J9" s="48"/>
       <c r="L9" s="74"/>
       <c r="M9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N9" s="74"/>
       <c r="O9" s="74"/>
@@ -6420,10 +6417,10 @@
       <c r="AD9" s="74"/>
       <c r="AE9" s="74"/>
       <c r="AF9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AH9" s="74"/>
       <c r="AI9" s="74"/>
@@ -6437,7 +6434,7 @@
       <c r="AQ9" s="74"/>
       <c r="AR9" s="74"/>
       <c r="AS9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AT9" s="74"/>
       <c r="AU9" s="74"/>
@@ -6509,7 +6506,7 @@
       <c r="DI9" s="74"/>
       <c r="DJ9" s="74"/>
       <c r="DK9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="DL9" s="74"/>
       <c r="DM9" s="74"/>
@@ -6551,13 +6548,13 @@
       <c r="EW9" s="74"/>
       <c r="EX9" s="74"/>
       <c r="EY9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="EZ9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="FA9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="FB9" s="74"/>
       <c r="FC9" s="74"/>
@@ -6566,17 +6563,17 @@
       <c r="FF9" s="74"/>
       <c r="FG9" s="74"/>
       <c r="FH9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="FI9" s="74"/>
       <c r="FJ9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="FK9" s="74"/>
       <c r="FL9" s="74"/>
       <c r="FM9" s="74"/>
       <c r="FN9" s="74" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="FO9" s="74"/>
       <c r="FP9" s="74"/>
@@ -6873,7 +6870,7 @@
         <v>373</v>
       </c>
       <c r="B11" s="65" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="66"/>
@@ -7111,7 +7108,7 @@
         <v>273</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>75</v>
@@ -7347,7 +7344,7 @@
         <v>374</v>
       </c>
       <c r="B13" s="65" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -7585,7 +7582,7 @@
         <v>274</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C14" s="51" t="s">
         <v>75</v>
@@ -7821,7 +7818,7 @@
         <v>375</v>
       </c>
       <c r="B15" s="65" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C15" s="66"/>
       <c r="D15" s="66"/>
@@ -8059,7 +8056,7 @@
         <v>275</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C16" s="51" t="s">
         <v>75</v>
@@ -8295,7 +8292,7 @@
         <v>376</v>
       </c>
       <c r="B17" s="65" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C17" s="66"/>
       <c r="D17" s="66"/>
@@ -8533,7 +8530,7 @@
         <v>276</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>75</v>
@@ -8766,10 +8763,10 @@
     </row>
     <row r="19" spans="1:221">
       <c r="A19" s="64" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B19" s="65" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C19" s="66"/>
       <c r="D19" s="66"/>
@@ -9007,7 +9004,7 @@
         <v>277</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>75</v>
@@ -9240,10 +9237,10 @@
     </row>
     <row r="21" spans="1:221">
       <c r="A21" s="64" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C21" s="66"/>
       <c r="D21" s="66"/>
@@ -9481,7 +9478,7 @@
         <v>278</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C22" s="51" t="s">
         <v>75</v>
@@ -9714,10 +9711,10 @@
     </row>
     <row r="23" spans="1:221">
       <c r="A23" s="64" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B23" s="65" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C23" s="66"/>
       <c r="D23" s="66"/>
@@ -9955,7 +9952,7 @@
         <v>279</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C24" s="51" t="s">
         <v>75</v>
@@ -10188,10 +10185,10 @@
     </row>
     <row r="25" spans="1:221">
       <c r="A25" s="64" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B25" s="65" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C25" s="66"/>
       <c r="D25" s="66"/>
@@ -10429,13 +10426,13 @@
         <v>280</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C26" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E26" s="52"/>
       <c r="F26" s="52"/>
@@ -10664,10 +10661,10 @@
     </row>
     <row r="27" spans="1:221">
       <c r="A27" s="64" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B27" s="65" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C27" s="66"/>
       <c r="D27" s="66"/>
@@ -10905,7 +10902,7 @@
         <v>281</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C28" s="51" t="s">
         <v>75</v>
@@ -11138,10 +11135,10 @@
     </row>
     <row r="29" spans="1:221">
       <c r="A29" s="64" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C29" s="66"/>
       <c r="D29" s="66"/>
@@ -11379,7 +11376,7 @@
         <v>282</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C30" s="51" t="s">
         <v>75</v>
@@ -11612,10 +11609,10 @@
     </row>
     <row r="31" spans="1:221">
       <c r="A31" s="59" t="s">
-        <v>377</v>
+        <v>268</v>
       </c>
       <c r="B31" s="60" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C31" s="61"/>
       <c r="D31" s="61"/>
@@ -11625,7 +11622,7 @@
       </c>
       <c r="F31" s="62">
         <f>IFERROR(IF(COUNT($F33:$F44)=0,"",_xlfn.MAXIFS($F33:$F44,$C33:$C44,"&lt;&gt;",$H33:$H44,"&lt;&gt;삭제")),"")</f>
-        <v>46157</v>
+        <v>46293</v>
       </c>
       <c r="G31" s="63">
         <f>IFERROR(AVERAGEIFS(G32:G44,$C32:$C44,"&lt;&gt;",$H32:$H44,"&lt;&gt;삭제"),0)</f>
@@ -11850,10 +11847,10 @@
     </row>
     <row r="32" spans="1:221">
       <c r="A32" s="64" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B32" s="65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C32" s="66"/>
       <c r="D32" s="66"/>
@@ -12091,13 +12088,13 @@
         <v>283</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C33" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E33" s="52"/>
       <c r="F33" s="52"/>
@@ -12329,13 +12326,13 @@
         <v>284</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C34" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E34" s="52"/>
       <c r="F34" s="52"/>
@@ -12564,10 +12561,10 @@
     </row>
     <row r="35" spans="1:221">
       <c r="A35" s="64" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B35" s="65" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C35" s="66"/>
       <c r="D35" s="66"/>
@@ -12805,13 +12802,13 @@
         <v>285</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C36" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E36" s="52">
         <v>46146</v>
@@ -13047,13 +13044,13 @@
         <v>286</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C37" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E37" s="52">
         <v>46146</v>
@@ -13286,10 +13283,10 @@
     </row>
     <row r="38" spans="1:221">
       <c r="A38" s="64" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B38" s="65" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C38" s="66"/>
       <c r="D38" s="66"/>
@@ -13527,13 +13524,13 @@
         <v>287</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E39" s="52">
         <v>46153</v>
@@ -13769,13 +13766,13 @@
         <v>288</v>
       </c>
       <c r="B40" s="50" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C40" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E40" s="52">
         <v>46153</v>
@@ -14008,10 +14005,10 @@
     </row>
     <row r="41" spans="1:221">
       <c r="A41" s="64" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B41" s="65" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C41" s="66"/>
       <c r="D41" s="66"/>
@@ -14249,13 +14246,13 @@
         <v>289</v>
       </c>
       <c r="B42" s="50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C42" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E42" s="52">
         <v>46153</v>
@@ -14488,20 +14485,20 @@
     </row>
     <row r="43" spans="1:221">
       <c r="A43" s="64" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B43" s="65" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C43" s="66"/>
       <c r="D43" s="66"/>
-      <c r="E43" s="67" t="str">
+      <c r="E43" s="67">
         <f>IFERROR(IF(COUNT($E44:$E44)=0,"",_xlfn.MINIFS($E44:$E44,$C44:$C44,"&lt;&gt;",$H44:$H44,"&lt;&gt;삭제")),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="67" t="str">
+        <v>46286</v>
+      </c>
+      <c r="F43" s="67">
         <f>IFERROR(IF(COUNT($F44:$F44)=0,"",_xlfn.MAXIFS($F44:$F44,$C44:$C44,"&lt;&gt;",$H44:$H44,"&lt;&gt;삭제")),"")</f>
-        <v/>
+        <v>46293</v>
       </c>
       <c r="G43" s="68">
         <f>IFERROR(AVERAGEIFS(G44:G44,$C44:$C44,"&lt;&gt;",$H44:$H44,"&lt;&gt;삭제"),0)</f>
@@ -14729,16 +14726,20 @@
         <v>290</v>
       </c>
       <c r="B44" s="50" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C44" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
+        <v>562</v>
+      </c>
+      <c r="E44" s="52">
+        <v>46286</v>
+      </c>
+      <c r="F44" s="52">
+        <v>46293</v>
+      </c>
       <c r="G44" s="53">
         <f>IF(OR($H44="삭제",$H44="작업대기",$H44="보류"),0,IF($H44="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E44)/($F44-$E44))),0)))</f>
         <v>0</v>
@@ -14964,7 +14965,7 @@
     </row>
     <row r="45" spans="1:221">
       <c r="A45" s="59" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B45" s="60" t="s">
         <v>107</v>
@@ -15202,10 +15203,10 @@
     </row>
     <row r="46" spans="1:221">
       <c r="A46" s="64" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B46" s="65" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C46" s="66"/>
       <c r="D46" s="66"/>
@@ -15443,13 +15444,13 @@
         <v>291</v>
       </c>
       <c r="B47" s="50" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C47" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E47" s="52"/>
       <c r="F47" s="52"/>
@@ -15681,13 +15682,13 @@
         <v>292</v>
       </c>
       <c r="B48" s="50" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C48" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D48" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E48" s="52"/>
       <c r="F48" s="52"/>
@@ -15919,13 +15920,13 @@
         <v>293</v>
       </c>
       <c r="B49" s="50" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C49" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E49" s="52"/>
       <c r="F49" s="52"/>
@@ -16154,10 +16155,10 @@
     </row>
     <row r="50" spans="1:221">
       <c r="A50" s="64" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B50" s="65" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C50" s="66"/>
       <c r="D50" s="66"/>
@@ -16395,13 +16396,13 @@
         <v>294</v>
       </c>
       <c r="B51" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C51" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E51" s="52"/>
       <c r="F51" s="52"/>
@@ -16633,13 +16634,13 @@
         <v>295</v>
       </c>
       <c r="B52" s="50" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C52" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D52" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E52" s="52"/>
       <c r="F52" s="52"/>
@@ -16871,13 +16872,13 @@
         <v>296</v>
       </c>
       <c r="B53" s="50" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C53" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D53" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E53" s="52"/>
       <c r="F53" s="52"/>
@@ -17106,10 +17107,10 @@
     </row>
     <row r="54" spans="1:221">
       <c r="A54" s="59" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B54" s="60" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C54" s="61"/>
       <c r="D54" s="61"/>
@@ -17122,11 +17123,11 @@
         <v>46280</v>
       </c>
       <c r="G54" s="63">
-        <f ca="1">IFERROR(AVERAGEIFS(G55:G68,$C55:$C68,"&lt;&gt;",$H55:$H68,"&lt;&gt;삭제"),0)</f>
-        <v>0.67045454545454541</v>
+        <f>IFERROR(AVERAGEIFS(G55:G68,$C55:$C68,"&lt;&gt;",$H55:$H68,"&lt;&gt;삭제"),0)</f>
+        <v>0.90909090909090906</v>
       </c>
       <c r="H54" s="61" t="str">
-        <f ca="1">IF($G54&gt;=1,"완료",IF($G54&gt;0,"진행중","작업대기"))</f>
+        <f>IF($G54&gt;=1,"완료",IF($G54&gt;0,"진행중","작업대기"))</f>
         <v>진행중</v>
       </c>
       <c r="I54" s="60"/>
@@ -17344,10 +17345,10 @@
     </row>
     <row r="55" spans="1:221">
       <c r="A55" s="64" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B55" s="65" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C55" s="66"/>
       <c r="D55" s="66"/>
@@ -17585,13 +17586,13 @@
         <v>297</v>
       </c>
       <c r="B56" s="50" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E56" s="52">
         <v>46209</v>
@@ -17827,13 +17828,13 @@
         <v>298</v>
       </c>
       <c r="B57" s="50" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C57" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E57" s="52">
         <v>46209</v>
@@ -18069,13 +18070,13 @@
         <v>299</v>
       </c>
       <c r="B58" s="50" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C58" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D58" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E58" s="52">
         <v>46209</v>
@@ -18308,10 +18309,10 @@
     </row>
     <row r="59" spans="1:221">
       <c r="A59" s="64" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B59" s="65" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C59" s="66"/>
       <c r="D59" s="66"/>
@@ -18549,13 +18550,13 @@
         <v>300</v>
       </c>
       <c r="B60" s="50" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C60" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D60" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E60" s="52">
         <v>46223</v>
@@ -18791,13 +18792,13 @@
         <v>301</v>
       </c>
       <c r="B61" s="50" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C61" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E61" s="52">
         <v>46223</v>
@@ -19033,13 +19034,13 @@
         <v>302</v>
       </c>
       <c r="B62" s="50" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C62" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D62" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E62" s="52">
         <v>46223</v>
@@ -19275,13 +19276,13 @@
         <v>303</v>
       </c>
       <c r="B63" s="50" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C63" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D63" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E63" s="52">
         <v>46237</v>
@@ -19514,10 +19515,10 @@
     </row>
     <row r="64" spans="1:221">
       <c r="A64" s="64" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B64" s="65" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C64" s="66"/>
       <c r="D64" s="66"/>
@@ -19530,11 +19531,11 @@
         <v>46280</v>
       </c>
       <c r="G64" s="68">
-        <f ca="1">IFERROR(AVERAGEIFS(G65:G68,$C65:$C68,"&lt;&gt;",$H65:$H68,"&lt;&gt;삭제"),0)</f>
-        <v>9.375E-2</v>
+        <f>IFERROR(AVERAGEIFS(G65:G68,$C65:$C68,"&lt;&gt;",$H65:$H68,"&lt;&gt;삭제"),0)</f>
+        <v>0.75</v>
       </c>
       <c r="H64" s="66" t="str">
-        <f ca="1">IF($G64&gt;=1,"완료",IF($G64&gt;0,"진행중","작업대기"))</f>
+        <f>IF($G64&gt;=1,"완료",IF($G64&gt;0,"진행중","작업대기"))</f>
         <v>진행중</v>
       </c>
       <c r="I64" s="65"/>
@@ -19755,13 +19756,13 @@
         <v>304</v>
       </c>
       <c r="B65" s="50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C65" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D65" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E65" s="52">
         <v>46272</v>
@@ -19770,11 +19771,11 @@
         <v>46280</v>
       </c>
       <c r="G65" s="53">
-        <f ca="1">IF(OR($H65="삭제",$H65="작업대기",$H65="보류"),0,IF($H65="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E65)/($F65-$E65))),0)))</f>
-        <v>0.125</v>
+        <f>IF(OR($H65="삭제",$H65="작업대기",$H65="보류"),0,IF($H65="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E65)/($F65-$E65))),0)))</f>
+        <v>1</v>
       </c>
       <c r="H65" s="51" t="s">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="I65" s="50" t="str">
         <f ca="1">IF(AND($F65&lt;&gt;"",$F65&lt;$F$3,$H65&lt;&gt;"완료",$H65&lt;&gt;"삭제",$H65&lt;&gt;"보류",$H65&lt;&gt;""),"⚠ 마감 초과",IF(AND($F65&lt;&gt;"",$F65&gt;$F$3,$H65="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -19997,13 +19998,13 @@
         <v>305</v>
       </c>
       <c r="B66" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C66" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D66" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E66" s="52">
         <v>46272</v>
@@ -20012,11 +20013,11 @@
         <v>46280</v>
       </c>
       <c r="G66" s="53">
-        <f ca="1">IF(OR($H66="삭제",$H66="작업대기",$H66="보류"),0,IF($H66="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E66)/($F66-$E66))),0)))</f>
-        <v>0.125</v>
+        <f>IF(OR($H66="삭제",$H66="작업대기",$H66="보류"),0,IF($H66="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E66)/($F66-$E66))),0)))</f>
+        <v>1</v>
       </c>
       <c r="H66" s="51" t="s">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="I66" s="50" t="str">
         <f ca="1">IF(AND($F66&lt;&gt;"",$F66&lt;$F$3,$H66&lt;&gt;"완료",$H66&lt;&gt;"삭제",$H66&lt;&gt;"보류",$H66&lt;&gt;""),"⚠ 마감 초과",IF(AND($F66&lt;&gt;"",$F66&gt;$F$3,$H66="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -20239,13 +20240,13 @@
         <v>306</v>
       </c>
       <c r="B67" s="50" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C67" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D67" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E67" s="52">
         <v>46272</v>
@@ -20254,11 +20255,11 @@
         <v>46280</v>
       </c>
       <c r="G67" s="53">
-        <f ca="1">IF(OR($H67="삭제",$H67="작업대기",$H67="보류"),0,IF($H67="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E67)/($F67-$E67))),0)))</f>
-        <v>0.125</v>
+        <f>IF(OR($H67="삭제",$H67="작업대기",$H67="보류"),0,IF($H67="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E67)/($F67-$E67))),0)))</f>
+        <v>1</v>
       </c>
       <c r="H67" s="51" t="s">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="I67" s="50" t="str">
         <f ca="1">IF(AND($F67&lt;&gt;"",$F67&lt;$F$3,$H67&lt;&gt;"완료",$H67&lt;&gt;"삭제",$H67&lt;&gt;"보류",$H67&lt;&gt;""),"⚠ 마감 초과",IF(AND($F67&lt;&gt;"",$F67&gt;$F$3,$H67="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -20481,13 +20482,13 @@
         <v>307</v>
       </c>
       <c r="B68" s="50" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C68" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D68" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E68" s="52"/>
       <c r="F68" s="52"/>
@@ -20496,7 +20497,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="51" t="s">
-        <v>106</v>
+        <v>369</v>
       </c>
       <c r="I68" s="50" t="str">
         <f ca="1">IF(AND($F68&lt;&gt;"",$F68&lt;$F$3,$H68&lt;&gt;"완료",$H68&lt;&gt;"삭제",$H68&lt;&gt;"보류",$H68&lt;&gt;""),"⚠ 마감 초과",IF(AND($F68&lt;&gt;"",$F68&gt;$F$3,$H68="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -20716,7 +20717,7 @@
     </row>
     <row r="69" spans="1:221">
       <c r="A69" s="59" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B69" s="60" t="s">
         <v>127</v>
@@ -20732,11 +20733,11 @@
         <v>46276</v>
       </c>
       <c r="G69" s="63">
-        <f ca="1">IFERROR(AVERAGEIFS(G70:G97,$C70:$C97,"&lt;&gt;",$H70:$H97,"&lt;&gt;삭제"),0)</f>
-        <v>0.60078512396694217</v>
+        <f>IFERROR(AVERAGEIFS(G70:G97,$C70:$C97,"&lt;&gt;",$H70:$H97,"&lt;&gt;삭제"),0)</f>
+        <v>0.68181818181818177</v>
       </c>
       <c r="H69" s="61" t="str">
-        <f ca="1">IF($G69&gt;=1,"완료",IF($G69&gt;0,"진행중","작업대기"))</f>
+        <f>IF($G69&gt;=1,"완료",IF($G69&gt;0,"진행중","작업대기"))</f>
         <v>진행중</v>
       </c>
       <c r="I69" s="60"/>
@@ -20954,10 +20955,10 @@
     </row>
     <row r="70" spans="1:221">
       <c r="A70" s="64" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C70" s="66"/>
       <c r="D70" s="66"/>
@@ -21195,13 +21196,13 @@
         <v>308</v>
       </c>
       <c r="B71" s="50" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C71" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D71" s="88" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E71" s="52">
         <v>46153</v>
@@ -21437,13 +21438,13 @@
         <v>309</v>
       </c>
       <c r="B72" s="50" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C72" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D72" s="88" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E72" s="52">
         <v>46153</v>
@@ -21679,13 +21680,13 @@
         <v>310</v>
       </c>
       <c r="B73" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C73" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D73" s="88" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E73" s="52">
         <v>46153</v>
@@ -21918,10 +21919,10 @@
     </row>
     <row r="74" spans="1:221">
       <c r="A74" s="64" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B74" s="65" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C74" s="66"/>
       <c r="D74" s="66"/>
@@ -22159,13 +22160,13 @@
         <v>311</v>
       </c>
       <c r="B75" s="50" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D75" s="88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E75" s="52"/>
       <c r="F75" s="52"/>
@@ -22397,13 +22398,13 @@
         <v>312</v>
       </c>
       <c r="B76" s="50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C76" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D76" s="88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E76" s="52"/>
       <c r="F76" s="52"/>
@@ -22635,13 +22636,13 @@
         <v>313</v>
       </c>
       <c r="B77" s="50" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C77" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D77" s="88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E77" s="52"/>
       <c r="F77" s="52"/>
@@ -22870,10 +22871,10 @@
     </row>
     <row r="78" spans="1:221">
       <c r="A78" s="64" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B78" s="65" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C78" s="66"/>
       <c r="D78" s="66"/>
@@ -22886,12 +22887,12 @@
         <v>46276</v>
       </c>
       <c r="G78" s="68">
-        <f ca="1">IFERROR(AVERAGEIFS(G79:G84,$C79:$C84,"&lt;&gt;",$H79:$H84,"&lt;&gt;삭제"),0)</f>
-        <v>0.95454545454545459</v>
+        <f>IFERROR(AVERAGEIFS(G79:G84,$C79:$C84,"&lt;&gt;",$H79:$H84,"&lt;&gt;삭제"),0)</f>
+        <v>1</v>
       </c>
       <c r="H78" s="66" t="str">
-        <f ca="1">IF($G78&gt;=1,"완료",IF($G78&gt;0,"진행중","작업대기"))</f>
-        <v>진행중</v>
+        <f>IF($G78&gt;=1,"완료",IF($G78&gt;0,"진행중","작업대기"))</f>
+        <v>완료</v>
       </c>
       <c r="I78" s="65"/>
       <c r="J78" s="65"/>
@@ -23111,10 +23112,10 @@
         <v>314</v>
       </c>
       <c r="B79" s="50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C79" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D79" s="66"/>
       <c r="E79" s="52">
@@ -23351,10 +23352,10 @@
         <v>315</v>
       </c>
       <c r="B80" s="50" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D80" s="66"/>
       <c r="E80" s="52">
@@ -23591,10 +23592,10 @@
         <v>316</v>
       </c>
       <c r="B81" s="50" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D81" s="66"/>
       <c r="E81" s="52">
@@ -23831,10 +23832,10 @@
         <v>317</v>
       </c>
       <c r="B82" s="50" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D82" s="66"/>
       <c r="E82" s="52">
@@ -24071,10 +24072,10 @@
         <v>318</v>
       </c>
       <c r="B83" s="50" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D83" s="66"/>
       <c r="E83" s="52">
@@ -24311,10 +24312,10 @@
         <v>319</v>
       </c>
       <c r="B84" s="50" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C84" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D84" s="51"/>
       <c r="E84" s="52">
@@ -24324,11 +24325,11 @@
         <v>46276</v>
       </c>
       <c r="G84" s="53">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.72727272727272729</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="H84" s="51" t="s">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="I84" s="50" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -24548,10 +24549,10 @@
     </row>
     <row r="85" spans="1:221">
       <c r="A85" s="64" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B85" s="65" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C85" s="66"/>
       <c r="D85" s="66"/>
@@ -24564,11 +24565,11 @@
         <v>46276</v>
       </c>
       <c r="G85" s="68">
-        <f ca="1">IFERROR(AVERAGEIFS(G86:G89,$C86:$C89,"&lt;&gt;",$H86:$H89,"&lt;&gt;삭제"),0)</f>
-        <v>0.3725</v>
+        <f>IFERROR(AVERAGEIFS(G86:G89,$C86:$C89,"&lt;&gt;",$H86:$H89,"&lt;&gt;삭제"),0)</f>
+        <v>0.75</v>
       </c>
       <c r="H85" s="66" t="str">
-        <f ca="1">IF($G85&gt;=1,"완료",IF($G85&gt;0,"진행중","작업대기"))</f>
+        <f>IF($G85&gt;=1,"완료",IF($G85&gt;0,"진행중","작업대기"))</f>
         <v>진행중</v>
       </c>
       <c r="I85" s="65"/>
@@ -24789,13 +24790,13 @@
         <v>320</v>
       </c>
       <c r="B86" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C86" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D86" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E86" s="52">
         <v>46272</v>
@@ -24804,11 +24805,11 @@
         <v>46276</v>
       </c>
       <c r="G86" s="53">
-        <f ca="1">IF(OR($H86="삭제",$H86="작업대기",$H86="보류"),0,IF($H86="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E86)/($F86-$E86))),0)))</f>
-        <v>0.25</v>
+        <f>IF(OR($H86="삭제",$H86="작업대기",$H86="보류"),0,IF($H86="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E86)/($F86-$E86))),0)))</f>
+        <v>1</v>
       </c>
       <c r="H86" s="51" t="s">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="I86" s="50" t="str">
         <f ca="1">IF(AND($F86&lt;&gt;"",$F86&lt;$F$3,$H86&lt;&gt;"완료",$H86&lt;&gt;"삭제",$H86&lt;&gt;"보류",$H86&lt;&gt;""),"⚠ 마감 초과",IF(AND($F86&lt;&gt;"",$F86&gt;$F$3,$H86="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -25031,13 +25032,13 @@
         <v>321</v>
       </c>
       <c r="B87" s="50" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C87" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D87" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E87" s="52">
         <v>46272</v>
@@ -25046,11 +25047,11 @@
         <v>46276</v>
       </c>
       <c r="G87" s="53">
-        <f ca="1">IF(OR($H87="삭제",$H87="작업대기",$H87="보류"),0,IF($H87="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E87)/($F87-$E87))),0)))</f>
-        <v>0.25</v>
+        <f>IF(OR($H87="삭제",$H87="작업대기",$H87="보류"),0,IF($H87="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E87)/($F87-$E87))),0)))</f>
+        <v>1</v>
       </c>
       <c r="H87" s="51" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="I87" s="50" t="str">
         <f ca="1">IF(AND($F87&lt;&gt;"",$F87&lt;$F$3,$H87&lt;&gt;"완료",$H87&lt;&gt;"삭제",$H87&lt;&gt;"보류",$H87&lt;&gt;""),"⚠ 마감 초과",IF(AND($F87&lt;&gt;"",$F87&gt;$F$3,$H87="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -25273,13 +25274,13 @@
         <v>322</v>
       </c>
       <c r="B88" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C88" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D88" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F88" s="52"/>
       <c r="G88" s="53">
@@ -25287,7 +25288,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="51" t="s">
-        <v>106</v>
+        <v>369</v>
       </c>
       <c r="I88" s="50" t="str">
         <f ca="1">IF(AND($F88&lt;&gt;"",$F88&lt;$F$3,$H88&lt;&gt;"완료",$H88&lt;&gt;"삭제",$H88&lt;&gt;"보류",$H88&lt;&gt;""),"⚠ 마감 초과",IF(AND($F88&lt;&gt;"",$F88&gt;$F$3,$H88="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -25510,13 +25511,13 @@
         <v>323</v>
       </c>
       <c r="B89" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C89" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D89" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E89" s="52">
         <v>46272</v>
@@ -25525,11 +25526,11 @@
         <v>46276</v>
       </c>
       <c r="G89" s="53">
-        <f ca="1">IF(OR($H89="삭제",$H89="작업대기",$H89="보류"),0,IF($H89="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E88)/($F89-$E88))),0)))</f>
-        <v>0.99</v>
+        <f>IF(OR($H89="삭제",$H89="작업대기",$H89="보류"),0,IF($H89="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E88)/($F89-$E88))),0)))</f>
+        <v>1</v>
       </c>
       <c r="H89" s="51" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="I89" s="50" t="str">
         <f ca="1">IF(AND($F89&lt;&gt;"",$F89&lt;$F$3,$H89&lt;&gt;"완료",$H89&lt;&gt;"삭제",$H89&lt;&gt;"보류",$H89&lt;&gt;""),"⚠ 마감 초과",IF(AND($F89&lt;&gt;"",$F89&gt;$F$3,$H89="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
@@ -25749,10 +25750,10 @@
     </row>
     <row r="90" spans="1:221">
       <c r="A90" s="64" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B90" s="65" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C90" s="66"/>
       <c r="D90" s="66"/>
@@ -25990,15 +25991,15 @@
         <v>324</v>
       </c>
       <c r="B91" s="50" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D91" s="88" t="s">
-        <v>573</v>
-      </c>
-      <c r="E91" s="109"/>
+        <v>572</v>
+      </c>
+      <c r="E91" s="89"/>
       <c r="F91" s="52"/>
       <c r="G91" s="53">
         <f>IF(OR($H91="삭제",$H91="작업대기",$H91="보류"),0,IF($H91="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E91)/($F91-$E91))),0)))</f>
@@ -26228,13 +26229,13 @@
         <v>325</v>
       </c>
       <c r="B92" s="50" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D92" s="88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E92" s="52"/>
       <c r="F92" s="52"/>
@@ -26466,13 +26467,13 @@
         <v>326</v>
       </c>
       <c r="B93" s="50" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D93" s="88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E93" s="52"/>
       <c r="F93" s="52"/>
@@ -26701,10 +26702,10 @@
     </row>
     <row r="94" spans="1:221">
       <c r="A94" s="64" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B94" s="65" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C94" s="66"/>
       <c r="D94" s="66"/>
@@ -26942,10 +26943,10 @@
         <v>327</v>
       </c>
       <c r="B95" s="50" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D95" s="66"/>
       <c r="E95" s="52"/>
@@ -27178,10 +27179,10 @@
         <v>328</v>
       </c>
       <c r="B96" s="50" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C96" s="51" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D96" s="66"/>
       <c r="E96" s="52"/>
@@ -27414,10 +27415,10 @@
         <v>329</v>
       </c>
       <c r="B97" s="50" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C97" s="51" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D97" s="66"/>
       <c r="E97" s="52"/>
@@ -27647,10 +27648,10 @@
     </row>
     <row r="98" spans="1:221">
       <c r="A98" s="59" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B98" s="60" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C98" s="61"/>
       <c r="D98" s="61"/>
@@ -27885,10 +27886,10 @@
     </row>
     <row r="99" spans="1:221">
       <c r="A99" s="64" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B99" s="65" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C99" s="66"/>
       <c r="D99" s="66"/>
@@ -28126,13 +28127,13 @@
         <v>330</v>
       </c>
       <c r="B100" s="50" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C100" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D100" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E100" s="52">
         <v>46244</v>
@@ -28368,13 +28369,13 @@
         <v>331</v>
       </c>
       <c r="B101" s="50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C101" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D101" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E101" s="52">
         <v>46244</v>
@@ -28610,13 +28611,13 @@
         <v>332</v>
       </c>
       <c r="B102" s="50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C102" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D102" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E102" s="52">
         <v>46244</v>
@@ -28849,10 +28850,10 @@
     </row>
     <row r="103" spans="1:221">
       <c r="A103" s="64" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B103" s="65" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C103" s="66"/>
       <c r="D103" s="66"/>
@@ -29090,13 +29091,13 @@
         <v>333</v>
       </c>
       <c r="B104" s="50" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C104" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D104" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E104" s="52">
         <v>46251</v>
@@ -29332,13 +29333,13 @@
         <v>334</v>
       </c>
       <c r="B105" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C105" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D105" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E105" s="52">
         <v>46251</v>
@@ -29574,13 +29575,13 @@
         <v>335</v>
       </c>
       <c r="B106" s="50" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C106" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D106" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E106" s="52">
         <v>46265</v>
@@ -29813,10 +29814,10 @@
     </row>
     <row r="107" spans="1:221">
       <c r="A107" s="64" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B107" s="65" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C107" s="66"/>
       <c r="D107" s="66"/>
@@ -30054,13 +30055,13 @@
         <v>336</v>
       </c>
       <c r="B108" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C108" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D108" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E108" s="52"/>
       <c r="F108" s="52"/>
@@ -30292,13 +30293,13 @@
         <v>337</v>
       </c>
       <c r="B109" s="50" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C109" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D109" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E109" s="52"/>
       <c r="F109" s="52"/>
@@ -30530,13 +30531,13 @@
         <v>338</v>
       </c>
       <c r="B110" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C110" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D110" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E110" s="52">
         <v>46265</v>
@@ -30769,7 +30770,7 @@
     </row>
     <row r="111" spans="1:221">
       <c r="A111" s="59" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B111" s="60" t="s">
         <v>158</v>
@@ -30786,7 +30787,7 @@
       </c>
       <c r="G111" s="63">
         <f ca="1">IFERROR(AVERAGEIFS(G112:G129,$C112:$C129,"&lt;&gt;",$H112:$H129,"&lt;&gt;삭제"),0)</f>
-        <v>0.52941176470588236</v>
+        <v>0.53769230769230769</v>
       </c>
       <c r="H111" s="61" t="str">
         <f ca="1">IF($G111&gt;=1,"완료",IF($G111&gt;0,"진행중","작업대기"))</f>
@@ -31007,10 +31008,10 @@
     </row>
     <row r="112" spans="1:221">
       <c r="A112" s="64" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B112" s="65" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C112" s="66"/>
       <c r="D112" s="66"/>
@@ -31248,13 +31249,13 @@
         <v>339</v>
       </c>
       <c r="B113" s="50" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C113" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D113" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E113" s="52"/>
       <c r="F113" s="52"/>
@@ -31486,13 +31487,13 @@
         <v>340</v>
       </c>
       <c r="B114" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C114" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D114" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E114" s="52"/>
       <c r="F114" s="52"/>
@@ -31721,10 +31722,10 @@
     </row>
     <row r="115" spans="1:221">
       <c r="A115" s="64" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B115" s="65" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C115" s="66"/>
       <c r="D115" s="66"/>
@@ -31738,7 +31739,7 @@
       </c>
       <c r="G115" s="68">
         <f ca="1">IFERROR(AVERAGEIFS(G116:G118,$C116:$C118,"&lt;&gt;",$H116:$H118,"&lt;&gt;삭제"),0)</f>
-        <v>0.96078431372549022</v>
+        <v>0.9966666666666667</v>
       </c>
       <c r="H115" s="66" t="str">
         <f ca="1">IF($G115&gt;=1,"완료",IF($G115&gt;0,"진행중","작업대기"))</f>
@@ -31962,13 +31963,13 @@
         <v>341</v>
       </c>
       <c r="B116" s="50" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C116" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D116" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E116" s="52">
         <v>46258</v>
@@ -31978,14 +31979,14 @@
       </c>
       <c r="G116" s="53">
         <f ca="1">IF(OR($H116="삭제",$H116="작업대기",$H116="보류"),0,IF($H116="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E116)/($F116-$E116))),0)))</f>
-        <v>0.88235294117647056</v>
+        <v>0.99</v>
       </c>
       <c r="H116" s="51" t="s">
         <v>209</v>
       </c>
       <c r="I116" s="50" t="str">
         <f ca="1">IF(AND($F116&lt;&gt;"",$F116&lt;$F$3,$H116&lt;&gt;"완료",$H116&lt;&gt;"삭제",$H116&lt;&gt;"보류",$H116&lt;&gt;""),"⚠ 마감 초과",IF(AND($F116&lt;&gt;"",$F116&gt;$F$3,$H116="완료"),"⚡ 미래 날짜 완료 이상",""))</f>
-        <v/>
+        <v>⚠ 마감 초과</v>
       </c>
       <c r="J116" s="50"/>
       <c r="L116" s="72"/>
@@ -32204,13 +32205,13 @@
         <v>342</v>
       </c>
       <c r="B117" s="50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C117" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D117" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E117" s="52">
         <v>46260</v>
@@ -32446,13 +32447,13 @@
         <v>343</v>
       </c>
       <c r="B118" s="50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C118" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D118" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E118" s="52">
         <v>46260</v>
@@ -32685,10 +32686,10 @@
     </row>
     <row r="119" spans="1:221">
       <c r="A119" s="64" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B119" s="65" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C119" s="66"/>
       <c r="D119" s="66"/>
@@ -32926,13 +32927,13 @@
         <v>344</v>
       </c>
       <c r="B120" s="50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C120" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D120" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E120" s="52">
         <v>46258</v>
@@ -33168,13 +33169,13 @@
         <v>345</v>
       </c>
       <c r="B121" s="50" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C121" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D121" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E121" s="52">
         <v>46258</v>
@@ -33410,13 +33411,13 @@
         <v>346</v>
       </c>
       <c r="B122" s="50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C122" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D122" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E122" s="52">
         <v>46258</v>
@@ -33649,10 +33650,10 @@
     </row>
     <row r="123" spans="1:221">
       <c r="A123" s="64" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B123" s="65" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C123" s="66"/>
       <c r="D123" s="66"/>
@@ -33890,13 +33891,13 @@
         <v>347</v>
       </c>
       <c r="B124" s="50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C124" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D124" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E124" s="52">
         <v>46263</v>
@@ -34132,13 +34133,13 @@
         <v>348</v>
       </c>
       <c r="B125" s="50" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C125" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D125" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E125" s="52">
         <v>46263</v>
@@ -34374,13 +34375,13 @@
         <v>349</v>
       </c>
       <c r="B126" s="50" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C126" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D126" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E126" s="50"/>
       <c r="F126" s="50"/>
@@ -34609,10 +34610,10 @@
     </row>
     <row r="127" spans="1:221">
       <c r="A127" s="64" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B127" s="65" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C127" s="66"/>
       <c r="D127" s="66"/>
@@ -34850,13 +34851,13 @@
         <v>350</v>
       </c>
       <c r="B128" s="50" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C128" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D128" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E128" s="52">
         <v>46279</v>
@@ -35092,13 +35093,13 @@
         <v>351</v>
       </c>
       <c r="B129" s="50" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C129" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D129" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E129" s="52">
         <v>46279</v>
@@ -35331,7 +35332,7 @@
     </row>
     <row r="130" spans="1:221">
       <c r="A130" s="59" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B130" s="60" t="s">
         <v>176</v>
@@ -35563,10 +35564,10 @@
     </row>
     <row r="131" spans="1:221">
       <c r="A131" s="64" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B131" s="65" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C131" s="66"/>
       <c r="D131" s="66"/>
@@ -35798,7 +35799,7 @@
         <v>352</v>
       </c>
       <c r="B132" s="50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C132" s="51" t="s">
         <v>75</v>
@@ -36034,13 +36035,13 @@
         <v>353</v>
       </c>
       <c r="B133" s="50" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C133" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D133" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E133" s="62"/>
       <c r="F133" s="62"/>
@@ -36272,7 +36273,7 @@
         <v>354</v>
       </c>
       <c r="B134" s="50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C134" s="51" t="s">
         <v>75</v>
@@ -36505,10 +36506,10 @@
     </row>
     <row r="135" spans="1:221">
       <c r="A135" s="64" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B135" s="65" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C135" s="66"/>
       <c r="D135" s="66"/>
@@ -36740,7 +36741,7 @@
         <v>355</v>
       </c>
       <c r="B136" s="50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C136" s="51" t="s">
         <v>75</v>
@@ -36973,7 +36974,7 @@
     </row>
     <row r="137" spans="1:221">
       <c r="A137" s="59" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B137" s="60" t="s">
         <v>183</v>
@@ -37205,10 +37206,10 @@
     </row>
     <row r="138" spans="1:221">
       <c r="A138" s="64" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B138" s="65" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C138" s="66"/>
       <c r="D138" s="66"/>
@@ -37440,16 +37441,20 @@
         <v>356</v>
       </c>
       <c r="B139" s="50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C139" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D139" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="E139" s="62"/>
-      <c r="F139" s="62"/>
+        <v>562</v>
+      </c>
+      <c r="E139" s="52">
+        <v>46286</v>
+      </c>
+      <c r="F139" s="52">
+        <v>46293</v>
+      </c>
       <c r="G139" s="53">
         <f>IF(OR($H139="삭제",$H139="작업대기",$H139="보류"),0,IF($H139="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E139)/($F139-$E139))),0)))</f>
         <v>0</v>
@@ -37678,16 +37683,20 @@
         <v>357</v>
       </c>
       <c r="B140" s="50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C140" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D140" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="E140" s="62"/>
-      <c r="F140" s="62"/>
+        <v>562</v>
+      </c>
+      <c r="E140" s="52">
+        <v>46286</v>
+      </c>
+      <c r="F140" s="52">
+        <v>46293</v>
+      </c>
       <c r="G140" s="53">
         <f>IF(OR($H140="삭제",$H140="작업대기",$H140="보류"),0,IF($H140="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E140)/($F140-$E140))),0)))</f>
         <v>0</v>
@@ -37916,16 +37925,20 @@
         <v>358</v>
       </c>
       <c r="B141" s="50" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C141" s="51" t="s">
         <v>146</v>
       </c>
       <c r="D141" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="E141" s="62"/>
-      <c r="F141" s="62"/>
+        <v>563</v>
+      </c>
+      <c r="E141" s="52">
+        <v>46286</v>
+      </c>
+      <c r="F141" s="52">
+        <v>46293</v>
+      </c>
       <c r="G141" s="53">
         <f>IF(OR($H141="삭제",$H141="작업대기",$H141="보류"),0,IF($H141="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E141)/($F141-$E141))),0)))</f>
         <v>0</v>
@@ -38154,16 +38167,20 @@
         <v>359</v>
       </c>
       <c r="B142" s="50" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C142" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D142" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="E142" s="62"/>
-      <c r="F142" s="62"/>
+        <v>562</v>
+      </c>
+      <c r="E142" s="52">
+        <v>46286</v>
+      </c>
+      <c r="F142" s="52">
+        <v>46293</v>
+      </c>
       <c r="G142" s="53">
         <f>IF(OR($H142="삭제",$H142="작업대기",$H142="보류"),0,IF($H142="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E142)/($F142-$E142))),0)))</f>
         <v>0</v>
@@ -38392,16 +38409,20 @@
         <v>360</v>
       </c>
       <c r="B143" s="50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C143" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D143" s="51" t="s">
-        <v>563</v>
-      </c>
-      <c r="E143" s="62"/>
-      <c r="F143" s="62"/>
+        <v>562</v>
+      </c>
+      <c r="E143" s="52">
+        <v>46286</v>
+      </c>
+      <c r="F143" s="52">
+        <v>46293</v>
+      </c>
       <c r="G143" s="53">
         <f>IF(OR($H143="삭제",$H143="작업대기",$H143="보류"),0,IF($H143="완료",1,IFERROR(MIN(0.99,MAX(0,($F$3-$E143)/($F143-$E143))),0)))</f>
         <v>0</v>
@@ -38627,7 +38648,7 @@
     </row>
     <row r="144" spans="1:221">
       <c r="A144" s="59" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B144" s="60" t="s">
         <v>190</v>
@@ -38652,7 +38673,7 @@
       </c>
       <c r="I144" s="60"/>
       <c r="J144" s="75" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L144" s="72"/>
       <c r="M144" s="72"/>
@@ -38867,10 +38888,10 @@
     </row>
     <row r="145" spans="1:221">
       <c r="A145" s="64" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B145" s="65" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C145" s="66"/>
       <c r="D145" s="66"/>
@@ -38892,7 +38913,7 @@
       </c>
       <c r="I145" s="65"/>
       <c r="J145" s="75" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L145" s="72"/>
       <c r="M145" s="72"/>
@@ -39110,7 +39131,7 @@
         <v>361</v>
       </c>
       <c r="B146" s="50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C146" s="51" t="s">
         <v>75</v>
@@ -39349,7 +39370,7 @@
         <v>362</v>
       </c>
       <c r="B147" s="50" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C147" s="51" t="s">
         <v>75</v>
@@ -39585,7 +39606,7 @@
         <v>363</v>
       </c>
       <c r="B148" s="50" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C148" s="51" t="s">
         <v>75</v>
@@ -39818,10 +39839,10 @@
     </row>
     <row r="149" spans="1:221">
       <c r="A149" s="64" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B149" s="65" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C149" s="66"/>
       <c r="D149" s="66"/>
@@ -40053,7 +40074,7 @@
         <v>364</v>
       </c>
       <c r="B150" s="50" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C150" s="51" t="s">
         <v>75</v>
@@ -40289,13 +40310,13 @@
         <v>365</v>
       </c>
       <c r="B151" s="50" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C151" s="51" t="s">
         <v>88</v>
       </c>
       <c r="D151" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E151" s="62"/>
       <c r="F151" s="62"/>
@@ -40527,7 +40548,7 @@
         <v>366</v>
       </c>
       <c r="B152" s="50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C152" s="51" t="s">
         <v>75</v>
@@ -40763,14 +40784,22 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="A88:D89 A90:J90 F91:J91 A91:D91 A92:J182 A10:J87 F88:J89">
+  <conditionalFormatting sqref="A88:D89 F88:J89 A90:J90 A91:D91 F91:J91 A10:J87 A92:J182">
     <cfRule type="expression" dxfId="34" priority="117">
       <formula>$H10="진행중"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A90:J90 A88:D89 F91:J91 A91:D91 A92:J182 A10:J87 F88:J89">
+  <conditionalFormatting sqref="F88:J89 A90:J90 F91:J91 A88:D89 A91:D91 A10:J87 A92:J182">
     <cfRule type="expression" dxfId="33" priority="115">
       <formula>$H10="완료"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E89">
+    <cfRule type="expression" dxfId="32" priority="1">
+      <formula>$H89="완료"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="2">
+      <formula>$H89="진행중"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G182">
@@ -40788,118 +40817,108 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I182">
-    <cfRule type="containsText" dxfId="32" priority="111" operator="containsText" text="마감 초과">
+    <cfRule type="containsText" dxfId="30" priority="111" operator="containsText" text="마감 초과">
       <formula>NOT(ISERROR(SEARCH("마감 초과",I10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="113" operator="containsText" text="미래">
+    <cfRule type="containsText" dxfId="29" priority="113" operator="containsText" text="미래">
       <formula>NOT(ISERROR(SEARCH("미래",I10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:HM9">
-    <cfRule type="expression" dxfId="30" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="147" stopIfTrue="1">
       <formula>AND(ROW()=8,L$7=$F$3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="149" stopIfTrue="1">
       <formula>OR(WEEKDAY(L$7,2)=6,WEEKDAY(L$7,2)=7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="151">
+    <cfRule type="expression" dxfId="26" priority="151">
       <formula>L$9="Y"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:HM87 L90:HM182">
-    <cfRule type="expression" dxfId="27" priority="171">
-      <formula>AND($C10="공통",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제")</formula>
+    <cfRule type="expression" dxfId="25" priority="169" stopIfTrue="1">
+      <formula>AND($C10="FE",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="157" stopIfTrue="1">
       <formula>AND($C10="",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제",OR($H10="완료",AND($H10="진행중",L$7=$E10)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="159" stopIfTrue="1">
       <formula>AND($C10="BE",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제",OR($H10="완료",AND($H10="진행중",L$7=$E10)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="161" stopIfTrue="1">
       <formula>AND($C10="FE",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제",OR($H10="완료",AND($H10="진행중",L$7=$E10)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="163" stopIfTrue="1">
       <formula>AND($C10="공통",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제",OR($H10="완료",AND($H10="진행중",L$7=$E10)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="165" stopIfTrue="1">
       <formula>AND($C10="",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="167" stopIfTrue="1">
       <formula>AND($C10="BE",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="169" stopIfTrue="1">
-      <formula>AND($C10="FE",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제")</formula>
+    <cfRule type="expression" dxfId="18" priority="171">
+      <formula>AND($C10="공통",$E10&lt;&gt;"",$J10&lt;&gt;"막대숨김",L$7&gt;=$E10,L$7&lt;=$F10,$H10&lt;&gt;"삭제")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:HM182">
-    <cfRule type="expression" dxfId="19" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="155" stopIfTrue="1">
       <formula>L$9="Y"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="153" stopIfTrue="1">
       <formula>OR(WEEKDAY(L$7,2)=6,WEEKDAY(L$7,2)=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L88:HM88">
-    <cfRule type="expression" dxfId="17" priority="181" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="181" stopIfTrue="1">
       <formula>AND($C88="BE",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제",OR($H88="완료",AND($H88="진행중",L$7=#REF!)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="178" stopIfTrue="1">
       <formula>AND($C88="",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제",OR($H88="완료",AND($H88="진행중",L$7=#REF!)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="184" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="184" stopIfTrue="1">
       <formula>AND($C88="FE",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제",OR($H88="완료",AND($H88="진행중",L$7=#REF!)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="187" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="187" stopIfTrue="1">
       <formula>AND($C88="공통",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제",OR($H88="완료",AND($H88="진행중",L$7=#REF!)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="190" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="190" stopIfTrue="1">
       <formula>AND($C88="",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="193" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="193" stopIfTrue="1">
       <formula>AND($C88="BE",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="196" stopIfTrue="1">
       <formula>AND($C88="FE",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="199">
+    <cfRule type="expression" dxfId="8" priority="199">
       <formula>AND($C88="공통",#REF!&lt;&gt;"",$J88&lt;&gt;"막대숨김",L$7&gt;=#REF!,L$7&lt;=$F88,$H88&lt;&gt;"삭제")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L89:HM89">
-    <cfRule type="expression" dxfId="9" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="180" stopIfTrue="1">
       <formula>AND($C89="BE",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제",OR($H89="완료",AND($H89="진행중",L$7=$E88)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="177" stopIfTrue="1">
       <formula>AND($C89="",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제",OR($H89="완료",AND($H89="진행중",L$7=$E88)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="183" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="183" stopIfTrue="1">
       <formula>AND($C89="FE",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제",OR($H89="완료",AND($H89="진행중",L$7=$E88)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="186" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="186" stopIfTrue="1">
       <formula>AND($C89="공통",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제",OR($H89="완료",AND($H89="진행중",L$7=$E88)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="189" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="189" stopIfTrue="1">
       <formula>AND($C89="",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="192" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="192" stopIfTrue="1">
       <formula>AND($C89="BE",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="195" stopIfTrue="1">
       <formula>AND($C89="FE",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="198">
+    <cfRule type="expression" dxfId="0" priority="198">
       <formula>AND($C89="공통",$E88&lt;&gt;"",$J89&lt;&gt;"막대숨김",L$7&gt;=$E88,L$7&lt;=$F89,$H89&lt;&gt;"삭제")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E89">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$H89="진행중"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E89">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$H89="완료"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -40947,284 +40966,284 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:217" ht="22" customHeight="1">
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="90" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="90" t="s">
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="92"/>
-      <c r="V1" s="90" t="s">
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="92"/>
-      <c r="AC1" s="90" t="s">
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
+      <c r="Z1" s="96"/>
+      <c r="AA1" s="96"/>
+      <c r="AB1" s="97"/>
+      <c r="AC1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="91"/>
-      <c r="AE1" s="91"/>
-      <c r="AF1" s="91"/>
-      <c r="AG1" s="91"/>
-      <c r="AH1" s="91"/>
-      <c r="AI1" s="92"/>
-      <c r="AJ1" s="90" t="s">
+      <c r="AD1" s="96"/>
+      <c r="AE1" s="96"/>
+      <c r="AF1" s="96"/>
+      <c r="AG1" s="96"/>
+      <c r="AH1" s="96"/>
+      <c r="AI1" s="97"/>
+      <c r="AJ1" s="95" t="s">
         <v>269</v>
       </c>
-      <c r="AK1" s="91"/>
-      <c r="AL1" s="91"/>
-      <c r="AM1" s="91"/>
-      <c r="AN1" s="91"/>
-      <c r="AO1" s="91"/>
-      <c r="AP1" s="92"/>
-      <c r="AQ1" s="90" t="s">
+      <c r="AK1" s="96"/>
+      <c r="AL1" s="96"/>
+      <c r="AM1" s="96"/>
+      <c r="AN1" s="96"/>
+      <c r="AO1" s="96"/>
+      <c r="AP1" s="97"/>
+      <c r="AQ1" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="AR1" s="91"/>
-      <c r="AS1" s="91"/>
-      <c r="AT1" s="91"/>
-      <c r="AU1" s="91"/>
-      <c r="AV1" s="91"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="90" t="s">
+      <c r="AR1" s="96"/>
+      <c r="AS1" s="96"/>
+      <c r="AT1" s="96"/>
+      <c r="AU1" s="96"/>
+      <c r="AV1" s="96"/>
+      <c r="AW1" s="97"/>
+      <c r="AX1" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="AY1" s="91"/>
-      <c r="AZ1" s="91"/>
-      <c r="BA1" s="91"/>
-      <c r="BB1" s="91"/>
-      <c r="BC1" s="91"/>
-      <c r="BD1" s="92"/>
-      <c r="BE1" s="90" t="s">
+      <c r="AY1" s="96"/>
+      <c r="AZ1" s="96"/>
+      <c r="BA1" s="96"/>
+      <c r="BB1" s="96"/>
+      <c r="BC1" s="96"/>
+      <c r="BD1" s="97"/>
+      <c r="BE1" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="BF1" s="91"/>
-      <c r="BG1" s="91"/>
-      <c r="BH1" s="91"/>
-      <c r="BI1" s="91"/>
-      <c r="BJ1" s="91"/>
-      <c r="BK1" s="92"/>
-      <c r="BL1" s="90" t="s">
+      <c r="BF1" s="96"/>
+      <c r="BG1" s="96"/>
+      <c r="BH1" s="96"/>
+      <c r="BI1" s="96"/>
+      <c r="BJ1" s="96"/>
+      <c r="BK1" s="97"/>
+      <c r="BL1" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="BM1" s="91"/>
-      <c r="BN1" s="91"/>
-      <c r="BO1" s="91"/>
-      <c r="BP1" s="91"/>
-      <c r="BQ1" s="91"/>
-      <c r="BR1" s="92"/>
-      <c r="BS1" s="90" t="s">
+      <c r="BM1" s="96"/>
+      <c r="BN1" s="96"/>
+      <c r="BO1" s="96"/>
+      <c r="BP1" s="96"/>
+      <c r="BQ1" s="96"/>
+      <c r="BR1" s="97"/>
+      <c r="BS1" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="BT1" s="91"/>
-      <c r="BU1" s="91"/>
-      <c r="BV1" s="91"/>
-      <c r="BW1" s="91"/>
-      <c r="BX1" s="91"/>
-      <c r="BY1" s="92"/>
-      <c r="BZ1" s="90" t="s">
+      <c r="BT1" s="96"/>
+      <c r="BU1" s="96"/>
+      <c r="BV1" s="96"/>
+      <c r="BW1" s="96"/>
+      <c r="BX1" s="96"/>
+      <c r="BY1" s="97"/>
+      <c r="BZ1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="CA1" s="91"/>
-      <c r="CB1" s="91"/>
-      <c r="CC1" s="91"/>
-      <c r="CD1" s="91"/>
-      <c r="CE1" s="91"/>
-      <c r="CF1" s="92"/>
-      <c r="CG1" s="90" t="s">
+      <c r="CA1" s="96"/>
+      <c r="CB1" s="96"/>
+      <c r="CC1" s="96"/>
+      <c r="CD1" s="96"/>
+      <c r="CE1" s="96"/>
+      <c r="CF1" s="97"/>
+      <c r="CG1" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="CH1" s="91"/>
-      <c r="CI1" s="91"/>
-      <c r="CJ1" s="91"/>
-      <c r="CK1" s="91"/>
-      <c r="CL1" s="91"/>
-      <c r="CM1" s="92"/>
-      <c r="CN1" s="90" t="s">
+      <c r="CH1" s="96"/>
+      <c r="CI1" s="96"/>
+      <c r="CJ1" s="96"/>
+      <c r="CK1" s="96"/>
+      <c r="CL1" s="96"/>
+      <c r="CM1" s="97"/>
+      <c r="CN1" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="CO1" s="91"/>
-      <c r="CP1" s="91"/>
-      <c r="CQ1" s="91"/>
-      <c r="CR1" s="91"/>
-      <c r="CS1" s="91"/>
-      <c r="CT1" s="92"/>
-      <c r="CU1" s="90" t="s">
+      <c r="CO1" s="96"/>
+      <c r="CP1" s="96"/>
+      <c r="CQ1" s="96"/>
+      <c r="CR1" s="96"/>
+      <c r="CS1" s="96"/>
+      <c r="CT1" s="97"/>
+      <c r="CU1" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="CV1" s="91"/>
-      <c r="CW1" s="91"/>
-      <c r="CX1" s="91"/>
-      <c r="CY1" s="91"/>
-      <c r="CZ1" s="91"/>
-      <c r="DA1" s="92"/>
-      <c r="DB1" s="90" t="s">
+      <c r="CV1" s="96"/>
+      <c r="CW1" s="96"/>
+      <c r="CX1" s="96"/>
+      <c r="CY1" s="96"/>
+      <c r="CZ1" s="96"/>
+      <c r="DA1" s="97"/>
+      <c r="DB1" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="DC1" s="91"/>
-      <c r="DD1" s="91"/>
-      <c r="DE1" s="91"/>
-      <c r="DF1" s="91"/>
-      <c r="DG1" s="91"/>
-      <c r="DH1" s="92"/>
-      <c r="DI1" s="90" t="s">
+      <c r="DC1" s="96"/>
+      <c r="DD1" s="96"/>
+      <c r="DE1" s="96"/>
+      <c r="DF1" s="96"/>
+      <c r="DG1" s="96"/>
+      <c r="DH1" s="97"/>
+      <c r="DI1" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="DJ1" s="91"/>
-      <c r="DK1" s="91"/>
-      <c r="DL1" s="91"/>
-      <c r="DM1" s="91"/>
-      <c r="DN1" s="91"/>
-      <c r="DO1" s="92"/>
-      <c r="DP1" s="90" t="s">
+      <c r="DJ1" s="96"/>
+      <c r="DK1" s="96"/>
+      <c r="DL1" s="96"/>
+      <c r="DM1" s="96"/>
+      <c r="DN1" s="96"/>
+      <c r="DO1" s="97"/>
+      <c r="DP1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="DQ1" s="91"/>
-      <c r="DR1" s="91"/>
-      <c r="DS1" s="91"/>
-      <c r="DT1" s="91"/>
-      <c r="DU1" s="91"/>
-      <c r="DV1" s="92"/>
-      <c r="DW1" s="90" t="s">
+      <c r="DQ1" s="96"/>
+      <c r="DR1" s="96"/>
+      <c r="DS1" s="96"/>
+      <c r="DT1" s="96"/>
+      <c r="DU1" s="96"/>
+      <c r="DV1" s="97"/>
+      <c r="DW1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="DX1" s="91"/>
-      <c r="DY1" s="91"/>
-      <c r="DZ1" s="91"/>
-      <c r="EA1" s="91"/>
-      <c r="EB1" s="91"/>
-      <c r="EC1" s="91"/>
-      <c r="ED1" s="90" t="s">
+      <c r="DX1" s="96"/>
+      <c r="DY1" s="96"/>
+      <c r="DZ1" s="96"/>
+      <c r="EA1" s="96"/>
+      <c r="EB1" s="96"/>
+      <c r="EC1" s="96"/>
+      <c r="ED1" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="EE1" s="91"/>
-      <c r="EF1" s="91"/>
-      <c r="EG1" s="91"/>
-      <c r="EH1" s="91"/>
-      <c r="EI1" s="91"/>
-      <c r="EJ1" s="91"/>
-      <c r="EK1" s="90" t="s">
+      <c r="EE1" s="96"/>
+      <c r="EF1" s="96"/>
+      <c r="EG1" s="96"/>
+      <c r="EH1" s="96"/>
+      <c r="EI1" s="96"/>
+      <c r="EJ1" s="96"/>
+      <c r="EK1" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="EL1" s="91"/>
-      <c r="EM1" s="91"/>
-      <c r="EN1" s="91"/>
-      <c r="EO1" s="91"/>
-      <c r="EP1" s="91"/>
-      <c r="EQ1" s="91"/>
-      <c r="ER1" s="90" t="s">
+      <c r="EL1" s="96"/>
+      <c r="EM1" s="96"/>
+      <c r="EN1" s="96"/>
+      <c r="EO1" s="96"/>
+      <c r="EP1" s="96"/>
+      <c r="EQ1" s="96"/>
+      <c r="ER1" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="ES1" s="91"/>
-      <c r="ET1" s="91"/>
-      <c r="EU1" s="91"/>
-      <c r="EV1" s="91"/>
-      <c r="EW1" s="91"/>
-      <c r="EX1" s="91"/>
-      <c r="EY1" s="90" t="s">
+      <c r="ES1" s="96"/>
+      <c r="ET1" s="96"/>
+      <c r="EU1" s="96"/>
+      <c r="EV1" s="96"/>
+      <c r="EW1" s="96"/>
+      <c r="EX1" s="96"/>
+      <c r="EY1" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="EZ1" s="91"/>
-      <c r="FA1" s="91"/>
-      <c r="FB1" s="91"/>
-      <c r="FC1" s="91"/>
-      <c r="FD1" s="91"/>
-      <c r="FE1" s="91"/>
-      <c r="FF1" s="90" t="s">
+      <c r="EZ1" s="96"/>
+      <c r="FA1" s="96"/>
+      <c r="FB1" s="96"/>
+      <c r="FC1" s="96"/>
+      <c r="FD1" s="96"/>
+      <c r="FE1" s="96"/>
+      <c r="FF1" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="FG1" s="91"/>
-      <c r="FH1" s="91"/>
-      <c r="FI1" s="91"/>
-      <c r="FJ1" s="91"/>
-      <c r="FK1" s="91"/>
-      <c r="FL1" s="91"/>
-      <c r="FM1" s="90" t="s">
+      <c r="FG1" s="96"/>
+      <c r="FH1" s="96"/>
+      <c r="FI1" s="96"/>
+      <c r="FJ1" s="96"/>
+      <c r="FK1" s="96"/>
+      <c r="FL1" s="96"/>
+      <c r="FM1" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="FN1" s="91"/>
-      <c r="FO1" s="91"/>
-      <c r="FP1" s="91"/>
-      <c r="FQ1" s="91"/>
-      <c r="FR1" s="91"/>
-      <c r="FS1" s="91"/>
-      <c r="FT1" s="90" t="s">
+      <c r="FN1" s="96"/>
+      <c r="FO1" s="96"/>
+      <c r="FP1" s="96"/>
+      <c r="FQ1" s="96"/>
+      <c r="FR1" s="96"/>
+      <c r="FS1" s="96"/>
+      <c r="FT1" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="FU1" s="91"/>
-      <c r="FV1" s="91"/>
-      <c r="FW1" s="91"/>
-      <c r="FX1" s="91"/>
-      <c r="FY1" s="91"/>
-      <c r="FZ1" s="91"/>
-      <c r="GA1" s="90" t="s">
+      <c r="FU1" s="96"/>
+      <c r="FV1" s="96"/>
+      <c r="FW1" s="96"/>
+      <c r="FX1" s="96"/>
+      <c r="FY1" s="96"/>
+      <c r="FZ1" s="96"/>
+      <c r="GA1" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="GB1" s="91"/>
-      <c r="GC1" s="91"/>
-      <c r="GD1" s="91"/>
-      <c r="GE1" s="91"/>
-      <c r="GF1" s="91"/>
-      <c r="GG1" s="91"/>
-      <c r="GH1" s="90" t="s">
+      <c r="GB1" s="96"/>
+      <c r="GC1" s="96"/>
+      <c r="GD1" s="96"/>
+      <c r="GE1" s="96"/>
+      <c r="GF1" s="96"/>
+      <c r="GG1" s="96"/>
+      <c r="GH1" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="GI1" s="91"/>
-      <c r="GJ1" s="91"/>
-      <c r="GK1" s="91"/>
-      <c r="GL1" s="91"/>
-      <c r="GM1" s="91"/>
-      <c r="GN1" s="91"/>
-      <c r="GO1" s="90" t="s">
+      <c r="GI1" s="96"/>
+      <c r="GJ1" s="96"/>
+      <c r="GK1" s="96"/>
+      <c r="GL1" s="96"/>
+      <c r="GM1" s="96"/>
+      <c r="GN1" s="96"/>
+      <c r="GO1" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="GP1" s="91"/>
-      <c r="GQ1" s="91"/>
-      <c r="GR1" s="91"/>
-      <c r="GS1" s="91"/>
-      <c r="GT1" s="91"/>
-      <c r="GU1" s="91"/>
-      <c r="GV1" s="90" t="s">
+      <c r="GP1" s="96"/>
+      <c r="GQ1" s="96"/>
+      <c r="GR1" s="96"/>
+      <c r="GS1" s="96"/>
+      <c r="GT1" s="96"/>
+      <c r="GU1" s="96"/>
+      <c r="GV1" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="GW1" s="91"/>
-      <c r="GX1" s="91"/>
-      <c r="GY1" s="91"/>
-      <c r="GZ1" s="91"/>
-      <c r="HA1" s="91"/>
-      <c r="HB1" s="91"/>
-      <c r="HC1" s="90" t="s">
+      <c r="GW1" s="96"/>
+      <c r="GX1" s="96"/>
+      <c r="GY1" s="96"/>
+      <c r="GZ1" s="96"/>
+      <c r="HA1" s="96"/>
+      <c r="HB1" s="96"/>
+      <c r="HC1" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="HD1" s="91"/>
-      <c r="HE1" s="91"/>
-      <c r="HF1" s="91"/>
-      <c r="HG1" s="91"/>
-      <c r="HH1" s="91"/>
-      <c r="HI1" s="91"/>
+      <c r="HD1" s="96"/>
+      <c r="HE1" s="96"/>
+      <c r="HF1" s="96"/>
+      <c r="HG1" s="96"/>
+      <c r="HH1" s="96"/>
+      <c r="HI1" s="96"/>
     </row>
     <row r="2" spans="1:217" ht="16" customHeight="1">
       <c r="G2" s="27"/>
@@ -42511,7 +42530,7 @@
       </c>
     </row>
     <row r="4" spans="1:217" ht="28" customHeight="1">
-      <c r="B4" s="93" t="s">
+      <c r="B4" s="98" t="s">
         <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -42531,7 +42550,7 @@
       </c>
     </row>
     <row r="5" spans="1:217" ht="28" customHeight="1">
-      <c r="B5" s="94"/>
+      <c r="B5" s="93"/>
       <c r="C5" s="2" t="s">
         <v>75</v>
       </c>
@@ -42549,7 +42568,7 @@
       </c>
     </row>
     <row r="6" spans="1:217" ht="28" customHeight="1">
-      <c r="B6" s="94"/>
+      <c r="B6" s="93"/>
       <c r="C6" s="2" t="s">
         <v>75</v>
       </c>
@@ -42567,7 +42586,7 @@
       </c>
     </row>
     <row r="7" spans="1:217" ht="28" customHeight="1">
-      <c r="B7" s="94"/>
+      <c r="B7" s="93"/>
       <c r="C7" s="2" t="s">
         <v>75</v>
       </c>
@@ -42585,7 +42604,7 @@
       </c>
     </row>
     <row r="8" spans="1:217" ht="28" customHeight="1">
-      <c r="B8" s="94"/>
+      <c r="B8" s="93"/>
       <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
@@ -42603,7 +42622,7 @@
       </c>
     </row>
     <row r="9" spans="1:217" ht="28" customHeight="1">
-      <c r="B9" s="94"/>
+      <c r="B9" s="93"/>
       <c r="C9" s="2" t="s">
         <v>75</v>
       </c>
@@ -42621,7 +42640,7 @@
       </c>
     </row>
     <row r="10" spans="1:217" ht="28" customHeight="1">
-      <c r="B10" s="94"/>
+      <c r="B10" s="93"/>
       <c r="C10" s="2" t="s">
         <v>75</v>
       </c>
@@ -42639,7 +42658,7 @@
       </c>
     </row>
     <row r="11" spans="1:217" ht="28" customHeight="1">
-      <c r="B11" s="94"/>
+      <c r="B11" s="93"/>
       <c r="C11" s="2" t="s">
         <v>88</v>
       </c>
@@ -42657,7 +42676,7 @@
       </c>
     </row>
     <row r="12" spans="1:217" ht="28" customHeight="1">
-      <c r="B12" s="94"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="2" t="s">
         <v>75</v>
       </c>
@@ -42675,7 +42694,7 @@
       </c>
     </row>
     <row r="13" spans="1:217" ht="28" customHeight="1">
-      <c r="B13" s="95"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="2" t="s">
         <v>75</v>
       </c>
@@ -42693,13 +42712,13 @@
       </c>
     </row>
     <row r="14" spans="1:217" ht="28" customHeight="1">
-      <c r="B14" s="93" t="s">
+      <c r="B14" s="98" t="s">
         <v>93</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="96" t="s">
+      <c r="D14" s="92" t="s">
         <v>94</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -42713,11 +42732,11 @@
       </c>
     </row>
     <row r="15" spans="1:217" ht="28" customHeight="1">
-      <c r="B15" s="94"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="95"/>
+      <c r="D15" s="94"/>
       <c r="E15" s="3" t="s">
         <v>96</v>
       </c>
@@ -42729,11 +42748,11 @@
       </c>
     </row>
     <row r="16" spans="1:217" ht="28" customHeight="1">
-      <c r="B16" s="94"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="96" t="s">
+      <c r="D16" s="92" t="s">
         <v>97</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -42754,11 +42773,11 @@
       <c r="BR16" s="37"/>
     </row>
     <row r="17" spans="2:95" ht="28" customHeight="1">
-      <c r="B17" s="94"/>
+      <c r="B17" s="93"/>
       <c r="C17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="95"/>
+      <c r="D17" s="94"/>
       <c r="E17" s="3" t="s">
         <v>99</v>
       </c>
@@ -42777,11 +42796,11 @@
       <c r="BR17" s="37"/>
     </row>
     <row r="18" spans="2:95" ht="28" customHeight="1">
-      <c r="B18" s="94"/>
+      <c r="B18" s="93"/>
       <c r="C18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="96" t="s">
+      <c r="D18" s="92" t="s">
         <v>100</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -42802,11 +42821,11 @@
       <c r="CA18" s="37"/>
     </row>
     <row r="19" spans="2:95" ht="28" customHeight="1">
-      <c r="B19" s="94"/>
+      <c r="B19" s="93"/>
       <c r="C19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="95"/>
+      <c r="D19" s="94"/>
       <c r="E19" s="3" t="s">
         <v>101</v>
       </c>
@@ -42825,7 +42844,7 @@
       <c r="CA19" s="37"/>
     </row>
     <row r="20" spans="2:95" ht="28" customHeight="1">
-      <c r="B20" s="94"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="2" t="s">
         <v>88</v>
       </c>
@@ -42850,7 +42869,7 @@
       <c r="CA20" s="37"/>
     </row>
     <row r="21" spans="2:95" ht="28" customHeight="1">
-      <c r="B21" s="95"/>
+      <c r="B21" s="94"/>
       <c r="C21" s="2" t="s">
         <v>88</v>
       </c>
@@ -42868,13 +42887,13 @@
       </c>
     </row>
     <row r="22" spans="2:95" ht="28" customHeight="1">
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="98" t="s">
         <v>107</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="96" t="s">
+      <c r="D22" s="92" t="s">
         <v>108</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -42888,11 +42907,11 @@
       </c>
     </row>
     <row r="23" spans="2:95" ht="28" customHeight="1">
-      <c r="B23" s="94"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="94"/>
+      <c r="D23" s="93"/>
       <c r="E23" s="3" t="s">
         <v>110</v>
       </c>
@@ -42904,11 +42923,11 @@
       </c>
     </row>
     <row r="24" spans="2:95" ht="28" customHeight="1">
-      <c r="B24" s="94"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="95"/>
+      <c r="D24" s="94"/>
       <c r="E24" s="3" t="s">
         <v>111</v>
       </c>
@@ -42920,11 +42939,11 @@
       </c>
     </row>
     <row r="25" spans="2:95" ht="28" customHeight="1">
-      <c r="B25" s="94"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="92" t="s">
         <v>112</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -42938,11 +42957,11 @@
       </c>
     </row>
     <row r="26" spans="2:95" ht="28" customHeight="1">
-      <c r="B26" s="94"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="94"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="3" t="s">
         <v>114</v>
       </c>
@@ -42954,11 +42973,11 @@
       </c>
     </row>
     <row r="27" spans="2:95" ht="28" customHeight="1">
-      <c r="B27" s="95"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="95"/>
+      <c r="D27" s="94"/>
       <c r="E27" s="3" t="s">
         <v>115</v>
       </c>
@@ -42970,13 +42989,13 @@
       </c>
     </row>
     <row r="28" spans="2:95" ht="28" customHeight="1">
-      <c r="B28" s="93" t="s">
+      <c r="B28" s="98" t="s">
         <v>116</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="96" t="s">
+      <c r="D28" s="92" t="s">
         <v>117</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -42997,11 +43016,11 @@
       <c r="CF28" s="37"/>
     </row>
     <row r="29" spans="2:95" ht="28" customHeight="1">
-      <c r="B29" s="94"/>
+      <c r="B29" s="93"/>
       <c r="C29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="94"/>
+      <c r="D29" s="93"/>
       <c r="E29" s="3" t="s">
         <v>228</v>
       </c>
@@ -43020,11 +43039,11 @@
       <c r="CF29" s="37"/>
     </row>
     <row r="30" spans="2:95" ht="28" customHeight="1">
-      <c r="B30" s="94"/>
+      <c r="B30" s="93"/>
       <c r="C30" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="95"/>
+      <c r="D30" s="94"/>
       <c r="E30" s="3" t="s">
         <v>229</v>
       </c>
@@ -43043,11 +43062,11 @@
       <c r="CF30" s="37"/>
     </row>
     <row r="31" spans="2:95" ht="28" customHeight="1">
-      <c r="B31" s="94"/>
+      <c r="B31" s="93"/>
       <c r="C31" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="96" t="s">
+      <c r="D31" s="92" t="s">
         <v>119</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -43069,11 +43088,11 @@
       <c r="CQ31" s="37"/>
     </row>
     <row r="32" spans="2:95" ht="28" customHeight="1">
-      <c r="B32" s="94"/>
+      <c r="B32" s="93"/>
       <c r="C32" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="94"/>
+      <c r="D32" s="93"/>
       <c r="E32" s="3" t="s">
         <v>121</v>
       </c>
@@ -43093,11 +43112,11 @@
       <c r="CQ32" s="37"/>
     </row>
     <row r="33" spans="2:131" ht="28" customHeight="1">
-      <c r="B33" s="94"/>
+      <c r="B33" s="93"/>
       <c r="C33" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="94"/>
+      <c r="D33" s="93"/>
       <c r="E33" s="3" t="s">
         <v>122</v>
       </c>
@@ -43116,11 +43135,11 @@
       <c r="CU33" s="37"/>
     </row>
     <row r="34" spans="2:131" ht="28" customHeight="1">
-      <c r="B34" s="94"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="95"/>
+      <c r="D34" s="94"/>
       <c r="E34" s="3" t="s">
         <v>123</v>
       </c>
@@ -43139,11 +43158,11 @@
       <c r="CU34" s="37"/>
     </row>
     <row r="35" spans="2:131" ht="28" customHeight="1">
-      <c r="B35" s="94"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="96" t="s">
+      <c r="D35" s="92" t="s">
         <v>124</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -43162,11 +43181,11 @@
       <c r="EA35" s="47"/>
     </row>
     <row r="36" spans="2:131" ht="28" customHeight="1">
-      <c r="B36" s="94"/>
+      <c r="B36" s="93"/>
       <c r="C36" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D36" s="94"/>
+      <c r="D36" s="93"/>
       <c r="E36" s="3" t="s">
         <v>125</v>
       </c>
@@ -43183,11 +43202,11 @@
       <c r="EA36" s="47"/>
     </row>
     <row r="37" spans="2:131" ht="28" customHeight="1">
-      <c r="B37" s="94"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="94"/>
+      <c r="D37" s="93"/>
       <c r="E37" s="3" t="s">
         <v>230</v>
       </c>
@@ -43204,11 +43223,11 @@
       <c r="EA37" s="47"/>
     </row>
     <row r="38" spans="2:131" ht="28" customHeight="1">
-      <c r="B38" s="95"/>
+      <c r="B38" s="94"/>
       <c r="C38" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="95"/>
+      <c r="D38" s="94"/>
       <c r="E38" s="3" t="s">
         <v>126</v>
       </c>
@@ -43220,13 +43239,13 @@
       </c>
     </row>
     <row r="39" spans="2:131" ht="28" customHeight="1">
-      <c r="B39" s="97" t="s">
+      <c r="B39" s="104" t="s">
         <v>127</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="96" t="s">
+      <c r="D39" s="92" t="s">
         <v>128</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -43252,11 +43271,11 @@
       <c r="AG39" s="37"/>
     </row>
     <row r="40" spans="2:131" ht="28" customHeight="1">
-      <c r="B40" s="98"/>
+      <c r="B40" s="105"/>
       <c r="C40" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="94"/>
+      <c r="D40" s="93"/>
       <c r="E40" s="3" t="s">
         <v>233</v>
       </c>
@@ -43280,11 +43299,11 @@
       <c r="AG40" s="37"/>
     </row>
     <row r="41" spans="2:131" ht="28" customHeight="1">
-      <c r="B41" s="98"/>
+      <c r="B41" s="105"/>
       <c r="C41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="95"/>
+      <c r="D41" s="94"/>
       <c r="E41" s="3" t="s">
         <v>221</v>
       </c>
@@ -43308,11 +43327,11 @@
       <c r="AG41" s="37"/>
     </row>
     <row r="42" spans="2:131" ht="28" customHeight="1">
-      <c r="B42" s="98"/>
+      <c r="B42" s="105"/>
       <c r="C42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="96" t="s">
+      <c r="D42" s="92" t="s">
         <v>129</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -43336,11 +43355,11 @@
       <c r="AI42" s="13"/>
     </row>
     <row r="43" spans="2:131" ht="28" customHeight="1">
-      <c r="B43" s="98"/>
+      <c r="B43" s="105"/>
       <c r="C43" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="94"/>
+      <c r="D43" s="93"/>
       <c r="E43" s="3" t="s">
         <v>130</v>
       </c>
@@ -43362,11 +43381,11 @@
       <c r="AI43" s="13"/>
     </row>
     <row r="44" spans="2:131" ht="28" customHeight="1">
-      <c r="B44" s="98"/>
+      <c r="B44" s="105"/>
       <c r="C44" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="95"/>
+      <c r="D44" s="94"/>
       <c r="E44" s="3" t="s">
         <v>223</v>
       </c>
@@ -43388,7 +43407,7 @@
       <c r="AI44" s="13"/>
     </row>
     <row r="45" spans="2:131" ht="28" customHeight="1">
-      <c r="B45" s="98"/>
+      <c r="B45" s="105"/>
       <c r="C45" s="2" t="s">
         <v>88</v>
       </c>
@@ -43416,7 +43435,7 @@
       <c r="DM45" s="41"/>
     </row>
     <row r="46" spans="2:131" ht="28" customHeight="1">
-      <c r="B46" s="98"/>
+      <c r="B46" s="105"/>
       <c r="C46" s="2" t="s">
         <v>88</v>
       </c>
@@ -43444,7 +43463,7 @@
       <c r="DX46" s="41"/>
     </row>
     <row r="47" spans="2:131" ht="28" customHeight="1">
-      <c r="B47" s="98"/>
+      <c r="B47" s="105"/>
       <c r="C47" s="2" t="s">
         <v>88</v>
       </c>
@@ -43472,7 +43491,7 @@
       <c r="DX47" s="41"/>
     </row>
     <row r="48" spans="2:131" ht="28" customHeight="1">
-      <c r="B48" s="98"/>
+      <c r="B48" s="105"/>
       <c r="C48" s="2" t="s">
         <v>88</v>
       </c>
@@ -43500,7 +43519,7 @@
       <c r="DX48" s="41"/>
     </row>
     <row r="49" spans="2:128" ht="28" customHeight="1">
-      <c r="B49" s="98"/>
+      <c r="B49" s="105"/>
       <c r="C49" s="2" t="s">
         <v>88</v>
       </c>
@@ -43528,7 +43547,7 @@
       <c r="DX49" s="41"/>
     </row>
     <row r="50" spans="2:128" ht="28" customHeight="1">
-      <c r="B50" s="98"/>
+      <c r="B50" s="105"/>
       <c r="C50" s="2" t="s">
         <v>88</v>
       </c>
@@ -43544,11 +43563,11 @@
       </c>
     </row>
     <row r="51" spans="2:128" ht="28" customHeight="1">
-      <c r="B51" s="98"/>
+      <c r="B51" s="105"/>
       <c r="C51" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D51" s="96" t="s">
+      <c r="D51" s="92" t="s">
         <v>132</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -43562,11 +43581,11 @@
       </c>
     </row>
     <row r="52" spans="2:128" ht="28" customHeight="1">
-      <c r="B52" s="98"/>
+      <c r="B52" s="105"/>
       <c r="C52" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D52" s="94"/>
+      <c r="D52" s="93"/>
       <c r="E52" s="3" t="s">
         <v>134</v>
       </c>
@@ -43578,11 +43597,11 @@
       </c>
     </row>
     <row r="53" spans="2:128" ht="28" customHeight="1">
-      <c r="B53" s="98"/>
+      <c r="B53" s="105"/>
       <c r="C53" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="94"/>
+      <c r="D53" s="93"/>
       <c r="E53" s="3" t="s">
         <v>135</v>
       </c>
@@ -43594,11 +43613,11 @@
       </c>
     </row>
     <row r="54" spans="2:128" ht="28" customHeight="1">
-      <c r="B54" s="98"/>
+      <c r="B54" s="105"/>
       <c r="C54" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="95"/>
+      <c r="D54" s="94"/>
       <c r="E54" s="3" t="s">
         <v>136</v>
       </c>
@@ -43610,11 +43629,11 @@
       </c>
     </row>
     <row r="55" spans="2:128" ht="28" customHeight="1">
-      <c r="B55" s="98"/>
+      <c r="B55" s="105"/>
       <c r="C55" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D55" s="96" t="s">
+      <c r="D55" s="92" t="s">
         <v>137</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -43628,11 +43647,11 @@
       </c>
     </row>
     <row r="56" spans="2:128" ht="28" customHeight="1">
-      <c r="B56" s="98"/>
+      <c r="B56" s="105"/>
       <c r="C56" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D56" s="94"/>
+      <c r="D56" s="93"/>
       <c r="E56" s="3" t="s">
         <v>139</v>
       </c>
@@ -43644,11 +43663,11 @@
       </c>
     </row>
     <row r="57" spans="2:128" ht="28" customHeight="1">
-      <c r="B57" s="98"/>
+      <c r="B57" s="105"/>
       <c r="C57" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="95"/>
+      <c r="D57" s="94"/>
       <c r="E57" s="3" t="s">
         <v>140</v>
       </c>
@@ -43660,11 +43679,11 @@
       </c>
     </row>
     <row r="58" spans="2:128" ht="28" customHeight="1">
-      <c r="B58" s="98"/>
+      <c r="B58" s="105"/>
       <c r="C58" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D58" s="96" t="s">
+      <c r="D58" s="92" t="s">
         <v>141</v>
       </c>
       <c r="E58" s="3" t="s">
@@ -43678,11 +43697,11 @@
       </c>
     </row>
     <row r="59" spans="2:128" ht="28" customHeight="1">
-      <c r="B59" s="98"/>
+      <c r="B59" s="105"/>
       <c r="C59" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D59" s="94"/>
+      <c r="D59" s="93"/>
       <c r="E59" s="3" t="s">
         <v>143</v>
       </c>
@@ -43694,11 +43713,11 @@
       </c>
     </row>
     <row r="60" spans="2:128" ht="28" customHeight="1">
-      <c r="B60" s="99"/>
+      <c r="B60" s="106"/>
       <c r="C60" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D60" s="95"/>
+      <c r="D60" s="94"/>
       <c r="E60" s="3" t="s">
         <v>144</v>
       </c>
@@ -43710,13 +43729,13 @@
       </c>
     </row>
     <row r="61" spans="2:128" ht="28" customHeight="1">
-      <c r="B61" s="103" t="s">
+      <c r="B61" s="107" t="s">
         <v>145</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D61" s="96" t="s">
+      <c r="D61" s="92" t="s">
         <v>147</v>
       </c>
       <c r="E61" s="3" t="s">
@@ -43734,11 +43753,11 @@
       <c r="DN61" s="17"/>
     </row>
     <row r="62" spans="2:128" ht="28" customHeight="1">
-      <c r="B62" s="104"/>
+      <c r="B62" s="108"/>
       <c r="C62" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D62" s="94"/>
+      <c r="D62" s="93"/>
       <c r="E62" s="3" t="s">
         <v>149</v>
       </c>
@@ -43754,11 +43773,11 @@
       <c r="DN62" s="17"/>
     </row>
     <row r="63" spans="2:128" ht="28" customHeight="1">
-      <c r="B63" s="104"/>
+      <c r="B63" s="108"/>
       <c r="C63" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D63" s="95"/>
+      <c r="D63" s="94"/>
       <c r="E63" s="3" t="s">
         <v>150</v>
       </c>
@@ -43774,11 +43793,11 @@
       <c r="DN63" s="40"/>
     </row>
     <row r="64" spans="2:128" ht="28" customHeight="1">
-      <c r="B64" s="104"/>
+      <c r="B64" s="108"/>
       <c r="C64" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D64" s="96" t="s">
+      <c r="D64" s="92" t="s">
         <v>151</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -43797,11 +43816,11 @@
       <c r="DR64" s="17"/>
     </row>
     <row r="65" spans="2:134" ht="28" customHeight="1">
-      <c r="B65" s="104"/>
+      <c r="B65" s="108"/>
       <c r="C65" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D65" s="94"/>
+      <c r="D65" s="93"/>
       <c r="E65" s="3" t="s">
         <v>153</v>
       </c>
@@ -43818,11 +43837,11 @@
       <c r="DR65" s="17"/>
     </row>
     <row r="66" spans="2:134" ht="28" customHeight="1">
-      <c r="B66" s="104"/>
+      <c r="B66" s="108"/>
       <c r="C66" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="95"/>
+      <c r="D66" s="94"/>
       <c r="E66" s="3" t="s">
         <v>154</v>
       </c>
@@ -43834,7 +43853,7 @@
       </c>
     </row>
     <row r="67" spans="2:134" ht="28" customHeight="1">
-      <c r="B67" s="104"/>
+      <c r="B67" s="108"/>
       <c r="C67" s="2" t="s">
         <v>146</v>
       </c>
@@ -43865,7 +43884,7 @@
       <c r="ED67" s="17"/>
     </row>
     <row r="68" spans="2:134" ht="28" customHeight="1">
-      <c r="B68" s="104"/>
+      <c r="B68" s="108"/>
       <c r="C68" s="2" t="s">
         <v>146</v>
       </c>
@@ -43881,7 +43900,7 @@
       </c>
     </row>
     <row r="69" spans="2:134" ht="28" customHeight="1">
-      <c r="B69" s="105"/>
+      <c r="B69" s="109"/>
       <c r="C69" s="2" t="s">
         <v>146</v>
       </c>
@@ -43900,13 +43919,13 @@
       <c r="ED69" s="17"/>
     </row>
     <row r="70" spans="2:134" ht="28" customHeight="1">
-      <c r="B70" s="103" t="s">
+      <c r="B70" s="107" t="s">
         <v>158</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D70" s="96" t="s">
+      <c r="D70" s="92" t="s">
         <v>159</v>
       </c>
       <c r="E70" s="3" t="s">
@@ -43920,11 +43939,11 @@
       </c>
     </row>
     <row r="71" spans="2:134" ht="28" customHeight="1">
-      <c r="B71" s="104"/>
+      <c r="B71" s="108"/>
       <c r="C71" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D71" s="95"/>
+      <c r="D71" s="94"/>
       <c r="E71" s="3" t="s">
         <v>161</v>
       </c>
@@ -43936,11 +43955,11 @@
       </c>
     </row>
     <row r="72" spans="2:134" ht="28" customHeight="1">
-      <c r="B72" s="104"/>
+      <c r="B72" s="108"/>
       <c r="C72" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D72" s="96" t="s">
+      <c r="D72" s="92" t="s">
         <v>162</v>
       </c>
       <c r="E72" s="3" t="s">
@@ -43962,11 +43981,11 @@
       <c r="DY72" s="17"/>
     </row>
     <row r="73" spans="2:134" ht="28" customHeight="1">
-      <c r="B73" s="104"/>
+      <c r="B73" s="108"/>
       <c r="C73" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D73" s="94"/>
+      <c r="D73" s="93"/>
       <c r="E73" s="3" t="s">
         <v>164</v>
       </c>
@@ -43986,11 +44005,11 @@
       <c r="DY73" s="17"/>
     </row>
     <row r="74" spans="2:134" ht="28" customHeight="1">
-      <c r="B74" s="104"/>
+      <c r="B74" s="108"/>
       <c r="C74" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D74" s="95"/>
+      <c r="D74" s="94"/>
       <c r="E74" s="3" t="s">
         <v>165</v>
       </c>
@@ -44010,11 +44029,11 @@
       <c r="DY74" s="40"/>
     </row>
     <row r="75" spans="2:134" ht="28" customHeight="1">
-      <c r="B75" s="104"/>
+      <c r="B75" s="108"/>
       <c r="C75" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D75" s="96" t="s">
+      <c r="D75" s="92" t="s">
         <v>166</v>
       </c>
       <c r="E75" s="3" t="s">
@@ -44032,11 +44051,11 @@
       <c r="EB75" s="17"/>
     </row>
     <row r="76" spans="2:134" ht="28" customHeight="1">
-      <c r="B76" s="104"/>
+      <c r="B76" s="108"/>
       <c r="C76" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D76" s="94"/>
+      <c r="D76" s="93"/>
       <c r="E76" s="3" t="s">
         <v>168</v>
       </c>
@@ -44048,11 +44067,11 @@
       </c>
     </row>
     <row r="77" spans="2:134" ht="28" customHeight="1">
-      <c r="B77" s="104"/>
+      <c r="B77" s="108"/>
       <c r="C77" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D77" s="95"/>
+      <c r="D77" s="94"/>
       <c r="E77" s="3" t="s">
         <v>169</v>
       </c>
@@ -44064,7 +44083,7 @@
       </c>
     </row>
     <row r="78" spans="2:134" ht="28" customHeight="1">
-      <c r="B78" s="104"/>
+      <c r="B78" s="108"/>
       <c r="C78" s="2" t="s">
         <v>146</v>
       </c>
@@ -44090,7 +44109,7 @@
       <c r="EB78" s="17"/>
     </row>
     <row r="79" spans="2:134" ht="28" customHeight="1">
-      <c r="B79" s="104"/>
+      <c r="B79" s="108"/>
       <c r="C79" s="2" t="s">
         <v>146</v>
       </c>
@@ -44114,7 +44133,7 @@
       <c r="EB79" s="40"/>
     </row>
     <row r="80" spans="2:134" ht="28" customHeight="1">
-      <c r="B80" s="104"/>
+      <c r="B80" s="108"/>
       <c r="C80" s="2" t="s">
         <v>146</v>
       </c>
@@ -44136,11 +44155,11 @@
       <c r="ED80" s="17"/>
     </row>
     <row r="81" spans="2:132" ht="28" customHeight="1">
-      <c r="B81" s="104"/>
+      <c r="B81" s="108"/>
       <c r="C81" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D81" s="96" t="s">
+      <c r="D81" s="92" t="s">
         <v>173</v>
       </c>
       <c r="E81" s="3" t="s">
@@ -44158,11 +44177,11 @@
       <c r="EB81" s="17"/>
     </row>
     <row r="82" spans="2:132" ht="28" customHeight="1">
-      <c r="B82" s="105"/>
+      <c r="B82" s="109"/>
       <c r="C82" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D82" s="95"/>
+      <c r="D82" s="94"/>
       <c r="E82" s="3" t="s">
         <v>175</v>
       </c>
@@ -44178,13 +44197,13 @@
       <c r="EB82" s="17"/>
     </row>
     <row r="83" spans="2:132" ht="28" customHeight="1">
-      <c r="B83" s="93" t="s">
+      <c r="B83" s="98" t="s">
         <v>176</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D83" s="96" t="s">
+      <c r="D83" s="92" t="s">
         <v>177</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -44206,11 +44225,11 @@
       <c r="BZ83" s="41"/>
     </row>
     <row r="84" spans="2:132" ht="28" customHeight="1">
-      <c r="B84" s="94"/>
+      <c r="B84" s="93"/>
       <c r="C84" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D84" s="94"/>
+      <c r="D84" s="93"/>
       <c r="E84" s="3" t="s">
         <v>179</v>
       </c>
@@ -44230,11 +44249,11 @@
       <c r="BZ84" s="37"/>
     </row>
     <row r="85" spans="2:132" ht="28" customHeight="1">
-      <c r="B85" s="94"/>
+      <c r="B85" s="93"/>
       <c r="C85" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D85" s="95"/>
+      <c r="D85" s="94"/>
       <c r="E85" s="3" t="s">
         <v>180</v>
       </c>
@@ -44254,7 +44273,7 @@
       <c r="BZ85" s="41"/>
     </row>
     <row r="86" spans="2:132" ht="28" customHeight="1">
-      <c r="B86" s="95"/>
+      <c r="B86" s="94"/>
       <c r="C86" s="2" t="s">
         <v>75</v>
       </c>
@@ -44280,13 +44299,13 @@
       <c r="CG86" s="41"/>
     </row>
     <row r="87" spans="2:132" ht="28" customHeight="1">
-      <c r="B87" s="93" t="s">
+      <c r="B87" s="98" t="s">
         <v>183</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D87" s="96" t="s">
+      <c r="D87" s="92" t="s">
         <v>184</v>
       </c>
       <c r="E87" s="3" t="s">
@@ -44308,11 +44327,11 @@
       <c r="CG87" s="37"/>
     </row>
     <row r="88" spans="2:132" ht="28" customHeight="1">
-      <c r="B88" s="94"/>
+      <c r="B88" s="93"/>
       <c r="C88" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D88" s="94"/>
+      <c r="D88" s="93"/>
       <c r="E88" s="3" t="s">
         <v>186</v>
       </c>
@@ -44332,11 +44351,11 @@
       <c r="CG88" s="37"/>
     </row>
     <row r="89" spans="2:132" ht="28" customHeight="1">
-      <c r="B89" s="94"/>
+      <c r="B89" s="93"/>
       <c r="C89" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D89" s="94"/>
+      <c r="D89" s="93"/>
       <c r="E89" s="3" t="s">
         <v>187</v>
       </c>
@@ -44356,11 +44375,11 @@
       <c r="CG89" s="17"/>
     </row>
     <row r="90" spans="2:132" ht="28" customHeight="1">
-      <c r="B90" s="94"/>
+      <c r="B90" s="93"/>
       <c r="C90" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D90" s="94"/>
+      <c r="D90" s="93"/>
       <c r="E90" s="3" t="s">
         <v>188</v>
       </c>
@@ -44380,11 +44399,11 @@
       <c r="CG90" s="37"/>
     </row>
     <row r="91" spans="2:132" ht="28" customHeight="1">
-      <c r="B91" s="95"/>
+      <c r="B91" s="94"/>
       <c r="C91" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D91" s="95"/>
+      <c r="D91" s="94"/>
       <c r="E91" s="3" t="s">
         <v>189</v>
       </c>
@@ -44404,13 +44423,13 @@
       <c r="CG91" s="37"/>
     </row>
     <row r="92" spans="2:132" ht="28" customHeight="1">
-      <c r="B92" s="93" t="s">
+      <c r="B92" s="98" t="s">
         <v>190</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D92" s="96" t="s">
+      <c r="D92" s="92" t="s">
         <v>191</v>
       </c>
       <c r="E92" s="3" t="s">
@@ -44427,11 +44446,11 @@
       <c r="Q92" s="41"/>
     </row>
     <row r="93" spans="2:132" ht="28" customHeight="1">
-      <c r="B93" s="94"/>
+      <c r="B93" s="93"/>
       <c r="C93" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D93" s="94"/>
+      <c r="D93" s="93"/>
       <c r="E93" s="3" t="s">
         <v>193</v>
       </c>
@@ -44451,11 +44470,11 @@
       <c r="CU93" s="41"/>
     </row>
     <row r="94" spans="2:132" ht="28" customHeight="1">
-      <c r="B94" s="94"/>
+      <c r="B94" s="93"/>
       <c r="C94" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D94" s="95"/>
+      <c r="D94" s="94"/>
       <c r="E94" s="3" t="s">
         <v>194</v>
       </c>
@@ -44475,11 +44494,11 @@
       <c r="CU94" s="41"/>
     </row>
     <row r="95" spans="2:132" ht="28" customHeight="1">
-      <c r="B95" s="94"/>
+      <c r="B95" s="93"/>
       <c r="C95" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D95" s="96" t="s">
+      <c r="D95" s="92" t="s">
         <v>195</v>
       </c>
       <c r="E95" s="3" t="s">
@@ -44501,11 +44520,11 @@
       <c r="CU95" s="41"/>
     </row>
     <row r="96" spans="2:132" ht="28" customHeight="1">
-      <c r="B96" s="94"/>
+      <c r="B96" s="93"/>
       <c r="C96" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D96" s="94"/>
+      <c r="D96" s="93"/>
       <c r="E96" s="3" t="s">
         <v>197</v>
       </c>
@@ -44525,11 +44544,11 @@
       <c r="CU96" s="37"/>
     </row>
     <row r="97" spans="2:99" ht="28" customHeight="1">
-      <c r="B97" s="95"/>
+      <c r="B97" s="94"/>
       <c r="C97" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D97" s="95"/>
+      <c r="D97" s="94"/>
       <c r="E97" s="3" t="s">
         <v>198</v>
       </c>
@@ -44549,14 +44568,14 @@
       <c r="CU97" s="41"/>
     </row>
     <row r="99" spans="2:99">
-      <c r="B99" s="89" t="s">
+      <c r="B99" s="103" t="s">
         <v>249</v>
       </c>
-      <c r="C99" s="89"/>
-      <c r="D99" s="89"/>
-      <c r="E99" s="89"/>
-      <c r="F99" s="89"/>
-      <c r="G99" s="89"/>
+      <c r="C99" s="103"/>
+      <c r="D99" s="103"/>
+      <c r="E99" s="103"/>
+      <c r="F99" s="103"/>
+      <c r="G99" s="103"/>
     </row>
     <row r="100" spans="2:99" ht="18">
       <c r="B100" s="30"/>
@@ -44684,26 +44703,37 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="CG1:CM1"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="D87:D91"/>
-    <mergeCell ref="ER1:EX1"/>
-    <mergeCell ref="DB1:DH1"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="EK1:EQ1"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D51:D54"/>
-    <mergeCell ref="AJ1:AP1"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="CN1:CT1"/>
-    <mergeCell ref="DP1:DV1"/>
-    <mergeCell ref="D75:D77"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="ED1:EJ1"/>
+    <mergeCell ref="B99:G99"/>
+    <mergeCell ref="HC1:HI1"/>
+    <mergeCell ref="DI1:DO1"/>
+    <mergeCell ref="B83:B86"/>
+    <mergeCell ref="BS1:BY1"/>
+    <mergeCell ref="D95:D97"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="DW1:EC1"/>
+    <mergeCell ref="AC1:AI1"/>
+    <mergeCell ref="GA1:GG1"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="B39:B60"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="B61:B69"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="B70:B82"/>
+    <mergeCell ref="B92:B97"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="CU1:DA1"/>
+    <mergeCell ref="FF1:FL1"/>
+    <mergeCell ref="EY1:FE1"/>
+    <mergeCell ref="O1:U1"/>
+    <mergeCell ref="V1:AB1"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="BE1:BK1"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="BL1:BR1"/>
     <mergeCell ref="GV1:HB1"/>
     <mergeCell ref="D83:D85"/>
     <mergeCell ref="AX1:BD1"/>
@@ -44720,38 +44750,27 @@
     <mergeCell ref="D31:D34"/>
     <mergeCell ref="BZ1:CF1"/>
     <mergeCell ref="AQ1:AW1"/>
+    <mergeCell ref="ER1:EX1"/>
+    <mergeCell ref="DB1:DH1"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="EK1:EQ1"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D51:D54"/>
+    <mergeCell ref="AJ1:AP1"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="CN1:CT1"/>
+    <mergeCell ref="DP1:DV1"/>
+    <mergeCell ref="D75:D77"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="ED1:EJ1"/>
     <mergeCell ref="D78:D80"/>
-    <mergeCell ref="B92:B97"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="CU1:DA1"/>
-    <mergeCell ref="FF1:FL1"/>
-    <mergeCell ref="EY1:FE1"/>
-    <mergeCell ref="O1:U1"/>
-    <mergeCell ref="V1:AB1"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="BE1:BK1"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="D61:D63"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="BL1:BR1"/>
-    <mergeCell ref="B99:G99"/>
-    <mergeCell ref="HC1:HI1"/>
-    <mergeCell ref="DI1:DO1"/>
-    <mergeCell ref="B83:B86"/>
-    <mergeCell ref="BS1:BY1"/>
-    <mergeCell ref="D95:D97"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="DW1:EC1"/>
-    <mergeCell ref="AC1:AI1"/>
-    <mergeCell ref="GA1:GG1"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="B39:B60"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="B61:B69"/>
-    <mergeCell ref="D67:D69"/>
-    <mergeCell ref="B70:B82"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="CG1:CM1"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="D87:D91"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
